--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1215"/>
+  <dimension ref="A1:U1237"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -65821,23 +65821,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1215" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1237" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1215" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1237" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1215" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1237" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1215" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1237" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1215" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1237" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68967,7 +68967,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1215" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1237" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69077,7 +69077,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1215" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1237" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -75763,11 +75763,11 @@
         <v>4046737.4413505867</v>
       </c>
       <c r="N1195">
-        <f t="shared" ref="N1195:N1215" si="155">IF(A1195&lt;&gt;$K$62,MAX(N1194,VLOOKUP(A1195,A:C,3)),)</f>
+        <f t="shared" ref="N1195:N1214" si="155">IF(A1195&lt;&gt;$K$62,MAX(N1194,VLOOKUP(A1195,A:C,3)),)</f>
         <v>1.2489999532699585</v>
       </c>
       <c r="O1195">
-        <f t="shared" ref="O1195:O1215" si="156">IF(A1195&lt;&gt;$K$62,MIN(O1194,VLOOKUP(A1195,A:D,4)),)</f>
+        <f t="shared" ref="O1195:O1214" si="156">IF(A1195&lt;&gt;$K$62,MIN(O1194,VLOOKUP(A1195,A:D,4)),)</f>
         <v>1.218000054359436</v>
       </c>
       <c r="P1195">
@@ -77023,12 +77023,12 @@
         <v>4026308.4497372219</v>
       </c>
       <c r="N1215">
-        <f t="shared" si="155"/>
-        <v>0</v>
+        <f>VLOOKUP(L63,A:C,3)</f>
+        <v>1.281999945640564</v>
       </c>
       <c r="O1215">
-        <f t="shared" si="156"/>
-        <v>0</v>
+        <f>VLOOKUP(L63,A:D,4)</f>
+        <v>1.253000020980835</v>
       </c>
       <c r="P1215">
         <f t="shared" si="143"/>
@@ -77053,6 +77053,1392 @@
       <c r="U1215">
         <f t="shared" si="136"/>
         <v>66.335527216233743</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1216" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1216">
+        <v>1.2799999713897705</v>
+      </c>
+      <c r="C1216">
+        <v>1.281999945640564</v>
+      </c>
+      <c r="D1216">
+        <v>1.253000020980835</v>
+      </c>
+      <c r="E1216">
+        <v>1.2640000581741333</v>
+      </c>
+      <c r="F1216">
+        <v>2671700</v>
+      </c>
+      <c r="G1216">
+        <v>26717</v>
+      </c>
+      <c r="H1216">
+        <f t="shared" si="144"/>
+        <v>1214</v>
+      </c>
+      <c r="I1216">
+        <f>SUM($F$3:F1216)/H1216</f>
+        <v>4025192.6272909804</v>
+      </c>
+      <c r="N1216">
+        <f t="shared" ref="N1216:N1237" si="157">IF(A1216&lt;&gt;$K$63,MAX(N1215,VLOOKUP(A1216,A:C,3)),)</f>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1216">
+        <f t="shared" ref="O1216:O1237" si="158">IF(A1216&lt;&gt;$K$63,MIN(O1215,VLOOKUP(A1216,A:D,4)),)</f>
+        <v>1.253000020980835</v>
+      </c>
+      <c r="P1216">
+        <f t="shared" si="143"/>
+        <v>1.2663333415985107</v>
+      </c>
+      <c r="Q1216">
+        <f t="shared" si="132"/>
+        <v>1.2485000065394811</v>
+      </c>
+      <c r="R1216">
+        <f t="shared" si="133"/>
+        <v>1.783333505902962E-2</v>
+      </c>
+      <c r="S1216">
+        <f t="shared" si="134"/>
+        <v>2.2214288614234134E-2</v>
+      </c>
+      <c r="T1216">
+        <f t="shared" si="135"/>
+        <v>3.33214329213512E-4</v>
+      </c>
+      <c r="U1216">
+        <f t="shared" si="136"/>
+        <v>53.519112161598095</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1217" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1217">
+        <v>1.2510000467300415</v>
+      </c>
+      <c r="C1217">
+        <v>1.2510000467300415</v>
+      </c>
+      <c r="D1217">
+        <v>1.2100000381469727</v>
+      </c>
+      <c r="E1217">
+        <v>1.2130000591278076</v>
+      </c>
+      <c r="F1217">
+        <v>2174700</v>
+      </c>
+      <c r="G1217">
+        <v>21747</v>
+      </c>
+      <c r="H1217">
+        <f t="shared" si="144"/>
+        <v>1215</v>
+      </c>
+      <c r="I1217">
+        <f>SUM($F$3:F1217)/H1217</f>
+        <v>4023669.5880915639</v>
+      </c>
+      <c r="N1217">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1217">
+        <f t="shared" si="158"/>
+        <v>1.2100000381469727</v>
+      </c>
+      <c r="P1217">
+        <f t="shared" si="143"/>
+        <v>1.2246667146682739</v>
+      </c>
+      <c r="Q1217">
+        <f t="shared" si="132"/>
+        <v>1.2512619154793876</v>
+      </c>
+      <c r="R1217">
+        <f t="shared" si="133"/>
+        <v>-2.6595200811113662E-2</v>
+      </c>
+      <c r="S1217">
+        <f t="shared" si="134"/>
+        <v>1.9034010212437637E-2</v>
+      </c>
+      <c r="T1217">
+        <f t="shared" si="135"/>
+        <v>2.8551015318656456E-4</v>
+      </c>
+      <c r="U1217">
+        <f t="shared" si="136"/>
+        <v>-93.149754971183881</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1218" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1218">
+        <v>1.1959999799728394</v>
+      </c>
+      <c r="C1218">
+        <v>1.2430000305175781</v>
+      </c>
+      <c r="D1218">
+        <v>1.1959999799728394</v>
+      </c>
+      <c r="E1218">
+        <v>1.2230000495910645</v>
+      </c>
+      <c r="F1218">
+        <v>1760400</v>
+      </c>
+      <c r="G1218">
+        <v>17604</v>
+      </c>
+      <c r="H1218">
+        <f t="shared" si="144"/>
+        <v>1216</v>
+      </c>
+      <c r="I1218">
+        <f>SUM($F$3:F1218)/H1218</f>
+        <v>4021808.3466539886</v>
+      </c>
+      <c r="N1218">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1218">
+        <f t="shared" si="158"/>
+        <v>1.1959999799728394</v>
+      </c>
+      <c r="P1218">
+        <f t="shared" si="143"/>
+        <v>1.2206666866938274</v>
+      </c>
+      <c r="Q1218">
+        <f t="shared" si="132"/>
+        <v>1.2529285833949135</v>
+      </c>
+      <c r="R1218">
+        <f t="shared" si="133"/>
+        <v>-3.2261896701086146E-2</v>
+      </c>
+      <c r="S1218">
+        <f t="shared" si="134"/>
+        <v>1.7309520925794328E-2</v>
+      </c>
+      <c r="T1218">
+        <f t="shared" si="135"/>
+        <v>2.5964281388691493E-4</v>
+      </c>
+      <c r="U1218">
+        <f t="shared" si="136"/>
+        <v>-124.25491858649137</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1219" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1219">
+        <v>1.2230000495910645</v>
+      </c>
+      <c r="C1219">
+        <v>1.2319999933242798</v>
+      </c>
+      <c r="D1219">
+        <v>1.2029999494552612</v>
+      </c>
+      <c r="E1219">
+        <v>1.2120000123977661</v>
+      </c>
+      <c r="F1219">
+        <v>1715600</v>
+      </c>
+      <c r="G1219">
+        <v>17156</v>
+      </c>
+      <c r="H1219">
+        <f t="shared" si="144"/>
+        <v>1217</v>
+      </c>
+      <c r="I1219">
+        <f>SUM($F$3:F1219)/H1219</f>
+        <v>4019913.3521209941</v>
+      </c>
+      <c r="N1219">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1219">
+        <f t="shared" si="158"/>
+        <v>1.1959999799728394</v>
+      </c>
+      <c r="P1219">
+        <f t="shared" si="143"/>
+        <v>1.215666651725769</v>
+      </c>
+      <c r="Q1219">
+        <f t="shared" si="132"/>
+        <v>1.2522857245944796</v>
+      </c>
+      <c r="R1219">
+        <f t="shared" si="133"/>
+        <v>-3.6619072868710578E-2</v>
+      </c>
+      <c r="S1219">
+        <f t="shared" si="134"/>
+        <v>1.7952379726228256E-2</v>
+      </c>
+      <c r="T1219">
+        <f t="shared" si="135"/>
+        <v>2.692856958934238E-4</v>
+      </c>
+      <c r="U1219">
+        <f t="shared" si="136"/>
+        <v>-135.98595628043847</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1220" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B1220">
+        <v>1.2170000076293945</v>
+      </c>
+      <c r="C1220">
+        <v>1.2170000076293945</v>
+      </c>
+      <c r="D1220">
+        <v>1.187999963760376</v>
+      </c>
+      <c r="E1220">
+        <v>1.2000000476837158</v>
+      </c>
+      <c r="F1220">
+        <v>3616800</v>
+      </c>
+      <c r="G1220">
+        <v>36168</v>
+      </c>
+      <c r="H1220">
+        <f t="shared" si="144"/>
+        <v>1218</v>
+      </c>
+      <c r="I1220">
+        <f>SUM($F$3:F1220)/H1220</f>
+        <v>4019582.3887777096</v>
+      </c>
+      <c r="N1220">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1220">
+        <f t="shared" si="158"/>
+        <v>1.187999963760376</v>
+      </c>
+      <c r="P1220">
+        <f t="shared" si="143"/>
+        <v>1.2016666730244954</v>
+      </c>
+      <c r="Q1220">
+        <f t="shared" si="132"/>
+        <v>1.2495000078564598</v>
+      </c>
+      <c r="R1220">
+        <f t="shared" si="133"/>
+        <v>-4.7833334831964391E-2</v>
+      </c>
+      <c r="S1220">
+        <f t="shared" si="134"/>
+        <v>2.1047618924355027E-2</v>
+      </c>
+      <c r="T1220">
+        <f t="shared" si="135"/>
+        <v>3.1571428386532538E-4</v>
+      </c>
+      <c r="U1220">
+        <f t="shared" si="136"/>
+        <v>-151.50830126003649</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1221" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B1221">
+        <v>1.1990000009536743</v>
+      </c>
+      <c r="C1221">
+        <v>1.2109999656677246</v>
+      </c>
+      <c r="D1221">
+        <v>1.1799999475479126</v>
+      </c>
+      <c r="E1221">
+        <v>1.184999942779541</v>
+      </c>
+      <c r="F1221">
+        <v>2669500</v>
+      </c>
+      <c r="G1221">
+        <v>26695</v>
+      </c>
+      <c r="H1221">
+        <f t="shared" si="144"/>
+        <v>1219</v>
+      </c>
+      <c r="I1221">
+        <f>SUM($F$3:F1221)/H1221</f>
+        <v>4018474.856055168</v>
+      </c>
+      <c r="N1221">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1221">
+        <f t="shared" si="158"/>
+        <v>1.1799999475479126</v>
+      </c>
+      <c r="P1221">
+        <f t="shared" si="143"/>
+        <v>1.1919999519983928</v>
+      </c>
+      <c r="Q1221">
+        <f t="shared" si="132"/>
+        <v>1.2454523841540019</v>
+      </c>
+      <c r="R1221">
+        <f t="shared" si="133"/>
+        <v>-5.3452432155609131E-2</v>
+      </c>
+      <c r="S1221">
+        <f t="shared" si="134"/>
+        <v>2.5673474584306973E-2</v>
+      </c>
+      <c r="T1221">
+        <f t="shared" si="135"/>
+        <v>3.8510211876460456E-4</v>
+      </c>
+      <c r="U1221">
+        <f t="shared" si="136"/>
+        <v>-138.80067013674929</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1222" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B1222">
+        <v>1.184999942779541</v>
+      </c>
+      <c r="C1222">
+        <v>1.2269999980926514</v>
+      </c>
+      <c r="D1222">
+        <v>1.1799999475479126</v>
+      </c>
+      <c r="E1222">
+        <v>1.2250000238418579</v>
+      </c>
+      <c r="F1222">
+        <v>3158901</v>
+      </c>
+      <c r="G1222">
+        <v>31589.009765625</v>
+      </c>
+      <c r="H1222">
+        <f t="shared" si="144"/>
+        <v>1220</v>
+      </c>
+      <c r="I1222">
+        <f>SUM($F$3:F1222)/H1222</f>
+        <v>4017770.2873206967</v>
+      </c>
+      <c r="N1222">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1222">
+        <f t="shared" si="158"/>
+        <v>1.1799999475479126</v>
+      </c>
+      <c r="P1222">
+        <f t="shared" si="143"/>
+        <v>1.2106666564941406</v>
+      </c>
+      <c r="Q1222">
+        <f t="shared" si="132"/>
+        <v>1.2412142895516893</v>
+      </c>
+      <c r="R1222">
+        <f t="shared" si="133"/>
+        <v>-3.0547633057548707E-2</v>
+      </c>
+      <c r="S1222">
+        <f t="shared" si="134"/>
+        <v>2.6404769647689088E-2</v>
+      </c>
+      <c r="T1222">
+        <f t="shared" si="135"/>
+        <v>3.9607154471533632E-4</v>
+      </c>
+      <c r="U1222">
+        <f t="shared" si="136"/>
+        <v>-77.126553182465642</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1223" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B1223">
+        <v>1.2250000238418579</v>
+      </c>
+      <c r="C1223">
+        <v>1.2319999933242798</v>
+      </c>
+      <c r="D1223">
+        <v>1.187999963760376</v>
+      </c>
+      <c r="E1223">
+        <v>1.187999963760376</v>
+      </c>
+      <c r="F1223">
+        <v>2479200</v>
+      </c>
+      <c r="G1223">
+        <v>24792</v>
+      </c>
+      <c r="H1223">
+        <f t="shared" si="144"/>
+        <v>1221</v>
+      </c>
+      <c r="I1223">
+        <f>SUM($F$3:F1223)/H1223</f>
+        <v>4016510.1969952909</v>
+      </c>
+      <c r="N1223">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1223">
+        <f t="shared" si="158"/>
+        <v>1.1799999475479126</v>
+      </c>
+      <c r="P1223">
+        <f t="shared" si="143"/>
+        <v>1.2026666402816772</v>
+      </c>
+      <c r="Q1223">
+        <f t="shared" si="132"/>
+        <v>1.2353333348319642</v>
+      </c>
+      <c r="R1223">
+        <f t="shared" si="133"/>
+        <v>-3.2666694550286923E-2</v>
+      </c>
+      <c r="S1223">
+        <f t="shared" si="134"/>
+        <v>2.5619052705310619E-2</v>
+      </c>
+      <c r="T1223">
+        <f t="shared" si="135"/>
+        <v>3.8428579057965924E-4</v>
+      </c>
+      <c r="U1223">
+        <f t="shared" si="136"/>
+        <v>-85.006251469803928</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1224" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B1224">
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="C1224">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="D1224">
+        <v>1.156999945640564</v>
+      </c>
+      <c r="E1224">
+        <v>1.1610000133514404</v>
+      </c>
+      <c r="F1224">
+        <v>4942000</v>
+      </c>
+      <c r="G1224">
+        <v>49420</v>
+      </c>
+      <c r="H1224">
+        <f t="shared" si="144"/>
+        <v>1222</v>
+      </c>
+      <c r="I1224">
+        <f>SUM($F$3:F1224)/H1224</f>
+        <v>4017267.5536262277</v>
+      </c>
+      <c r="N1224">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1224">
+        <f t="shared" si="158"/>
+        <v>1.156999945640564</v>
+      </c>
+      <c r="P1224">
+        <f t="shared" si="143"/>
+        <v>1.1696666479110718</v>
+      </c>
+      <c r="Q1224">
+        <f t="shared" si="132"/>
+        <v>1.2285714291390917</v>
+      </c>
+      <c r="R1224">
+        <f t="shared" si="133"/>
+        <v>-5.8904781228019898E-2</v>
+      </c>
+      <c r="S1224">
+        <f t="shared" si="134"/>
+        <v>2.7272115759298061E-2</v>
+      </c>
+      <c r="T1224">
+        <f t="shared" si="135"/>
+        <v>4.0908173638947088E-4</v>
+      </c>
+      <c r="U1224">
+        <f t="shared" si="136"/>
+        <v>-143.99269385113524</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1225" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B1225">
+        <v>1.1649999618530273</v>
+      </c>
+      <c r="C1225">
+        <v>1.1979999542236328</v>
+      </c>
+      <c r="D1225">
+        <v>1.156000018119812</v>
+      </c>
+      <c r="E1225">
+        <v>1.1970000267028809</v>
+      </c>
+      <c r="F1225">
+        <v>4192600</v>
+      </c>
+      <c r="G1225">
+        <v>41926</v>
+      </c>
+      <c r="H1225">
+        <f t="shared" si="144"/>
+        <v>1223</v>
+      </c>
+      <c r="I1225">
+        <f>SUM($F$3:F1225)/H1225</f>
+        <v>4017410.9162152493</v>
+      </c>
+      <c r="N1225">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1225">
+        <f t="shared" si="158"/>
+        <v>1.156000018119812</v>
+      </c>
+      <c r="P1225">
+        <f t="shared" si="143"/>
+        <v>1.1836666663487752</v>
+      </c>
+      <c r="Q1225">
+        <f t="shared" si="132"/>
+        <v>1.2234523807253157</v>
+      </c>
+      <c r="R1225">
+        <f t="shared" si="133"/>
+        <v>-3.9785714376540549E-2</v>
+      </c>
+      <c r="S1225">
+        <f t="shared" si="134"/>
+        <v>2.7278924474910808E-2</v>
+      </c>
+      <c r="T1225">
+        <f t="shared" si="135"/>
+        <v>4.0918386712366213E-4</v>
+      </c>
+      <c r="U1225">
+        <f t="shared" si="136"/>
+        <v>-97.23187440456114</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1226" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B1226">
+        <v>1.2020000219345093</v>
+      </c>
+      <c r="C1226">
+        <v>1.2100000381469727</v>
+      </c>
+      <c r="D1226">
+        <v>1.190000057220459</v>
+      </c>
+      <c r="E1226">
+        <v>1.1929999589920044</v>
+      </c>
+      <c r="F1226">
+        <v>3501201.25</v>
+      </c>
+      <c r="G1226">
+        <v>35012.01171875</v>
+      </c>
+      <c r="H1226">
+        <f t="shared" si="144"/>
+        <v>1224</v>
+      </c>
+      <c r="I1226">
+        <f>SUM($F$3:F1226)/H1226</f>
+        <v>4016989.1762918709</v>
+      </c>
+      <c r="N1226">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1226">
+        <f t="shared" si="158"/>
+        <v>1.156000018119812</v>
+      </c>
+      <c r="P1226">
+        <f t="shared" si="143"/>
+        <v>1.1976666847864788</v>
+      </c>
+      <c r="Q1226">
+        <f t="shared" si="132"/>
+        <v>1.2174285707019623</v>
+      </c>
+      <c r="R1226">
+        <f t="shared" si="133"/>
+        <v>-1.9761885915483557E-2</v>
+      </c>
+      <c r="S1226">
+        <f t="shared" si="134"/>
+        <v>2.368028472069978E-2</v>
+      </c>
+      <c r="T1226">
+        <f t="shared" si="135"/>
+        <v>3.5520427081049672E-4</v>
+      </c>
+      <c r="U1226">
+        <f t="shared" si="136"/>
+        <v>-55.635271136778151</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1227" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B1227">
+        <v>1.1829999685287476</v>
+      </c>
+      <c r="C1227">
+        <v>1.1950000524520874</v>
+      </c>
+      <c r="D1227">
+        <v>1.1649999618530273</v>
+      </c>
+      <c r="E1227">
+        <v>1.1749999523162842</v>
+      </c>
+      <c r="F1227">
+        <v>2815900</v>
+      </c>
+      <c r="G1227">
+        <v>28159</v>
+      </c>
+      <c r="H1227">
+        <f t="shared" si="144"/>
+        <v>1225</v>
+      </c>
+      <c r="I1227">
+        <f>SUM($F$3:F1227)/H1227</f>
+        <v>4016008.6953316326</v>
+      </c>
+      <c r="N1227">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1227">
+        <f t="shared" si="158"/>
+        <v>1.156000018119812</v>
+      </c>
+      <c r="P1227">
+        <f t="shared" si="143"/>
+        <v>1.178333322207133</v>
+      </c>
+      <c r="Q1227">
+        <f t="shared" si="132"/>
+        <v>1.2121904747826713</v>
+      </c>
+      <c r="R1227">
+        <f t="shared" si="133"/>
+        <v>-3.385715257553823E-2</v>
+      </c>
+      <c r="S1227">
+        <f t="shared" si="134"/>
+        <v>2.3027222172743604E-2</v>
+      </c>
+      <c r="T1227">
+        <f t="shared" si="135"/>
+        <v>3.4540833259115406E-4</v>
+      </c>
+      <c r="U1227">
+        <f t="shared" si="136"/>
+        <v>-98.020659552569555</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1228" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B1228">
+        <v>1.1629999876022339</v>
+      </c>
+      <c r="C1228">
+        <v>1.1629999876022339</v>
+      </c>
+      <c r="D1228">
+        <v>1.1059999465942383</v>
+      </c>
+      <c r="E1228">
+        <v>1.1160000562667847</v>
+      </c>
+      <c r="F1228">
+        <v>4126103</v>
+      </c>
+      <c r="G1228">
+        <v>41261.03125</v>
+      </c>
+      <c r="H1228">
+        <f t="shared" si="144"/>
+        <v>1226</v>
+      </c>
+      <c r="I1228">
+        <f>SUM($F$3:F1228)/H1228</f>
+        <v>4016098.4949276103</v>
+      </c>
+      <c r="N1228">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1228">
+        <f t="shared" si="158"/>
+        <v>1.1059999465942383</v>
+      </c>
+      <c r="P1228">
+        <f t="shared" si="143"/>
+        <v>1.1283333301544189</v>
+      </c>
+      <c r="Q1228">
+        <f t="shared" si="132"/>
+        <v>1.2043333337420508</v>
+      </c>
+      <c r="R1228">
+        <f t="shared" si="133"/>
+        <v>-7.6000003587631815E-2</v>
+      </c>
+      <c r="S1228">
+        <f t="shared" si="134"/>
+        <v>2.5809536174851995E-2</v>
+      </c>
+      <c r="T1228">
+        <f t="shared" si="135"/>
+        <v>3.8714304262277993E-4</v>
+      </c>
+      <c r="U1228">
+        <f t="shared" si="136"/>
+        <v>-196.30987831462554</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1229" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B1229">
+        <v>1.1319999694824219</v>
+      </c>
+      <c r="C1229">
+        <v>1.1430000066757202</v>
+      </c>
+      <c r="D1229">
+        <v>1.1000000238418579</v>
+      </c>
+      <c r="E1229">
+        <v>1.1239999532699585</v>
+      </c>
+      <c r="F1229">
+        <v>5773200</v>
+      </c>
+      <c r="G1229">
+        <v>57732</v>
+      </c>
+      <c r="H1229">
+        <f t="shared" si="144"/>
+        <v>1227</v>
+      </c>
+      <c r="I1229">
+        <f>SUM($F$3:F1229)/H1229</f>
+        <v>4017530.5254940912</v>
+      </c>
+      <c r="N1229">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1229">
+        <f t="shared" si="158"/>
+        <v>1.1000000238418579</v>
+      </c>
+      <c r="P1229">
+        <f t="shared" si="143"/>
+        <v>1.1223333279291789</v>
+      </c>
+      <c r="Q1229">
+        <f t="shared" si="132"/>
+        <v>1.1938809497015817</v>
+      </c>
+      <c r="R1229">
+        <f t="shared" si="133"/>
+        <v>-7.1547621772402703E-2</v>
+      </c>
+      <c r="S1229">
+        <f t="shared" si="134"/>
+        <v>2.699320738007422E-2</v>
+      </c>
+      <c r="T1229">
+        <f t="shared" si="135"/>
+        <v>4.0489811070111331E-4</v>
+      </c>
+      <c r="U1229">
+        <f t="shared" si="136"/>
+        <v>-176.70524974421912</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1230" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B1230">
+        <v>1.125</v>
+      </c>
+      <c r="C1230">
+        <v>1.1740000247955322</v>
+      </c>
+      <c r="D1230">
+        <v>1.1089999675750732</v>
+      </c>
+      <c r="E1230">
+        <v>1.1720000505447388</v>
+      </c>
+      <c r="F1230">
+        <v>5936101</v>
+      </c>
+      <c r="G1230">
+        <v>59361.01171875</v>
+      </c>
+      <c r="H1230">
+        <f t="shared" si="144"/>
+        <v>1228</v>
+      </c>
+      <c r="I1230">
+        <f>SUM($F$3:F1230)/H1230</f>
+        <v>4019092.8793006921</v>
+      </c>
+      <c r="N1230">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1230">
+        <f t="shared" si="158"/>
+        <v>1.1000000238418579</v>
+      </c>
+      <c r="P1230">
+        <f t="shared" si="143"/>
+        <v>1.1516666809717815</v>
+      </c>
+      <c r="Q1230">
+        <f t="shared" si="132"/>
+        <v>1.1856904739425296</v>
+      </c>
+      <c r="R1230">
+        <f t="shared" si="133"/>
+        <v>-3.402379297074809E-2</v>
+      </c>
+      <c r="S1230">
+        <f t="shared" si="134"/>
+        <v>2.5734695447545475E-2</v>
+      </c>
+      <c r="T1230">
+        <f t="shared" si="135"/>
+        <v>3.8602043171318212E-4</v>
+      </c>
+      <c r="U1230">
+        <f t="shared" si="136"/>
+        <v>-88.139875963944263</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1231" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B1231">
+        <v>1.1599999666213989</v>
+      </c>
+      <c r="C1231">
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="D1231">
+        <v>1.1469999551773071</v>
+      </c>
+      <c r="E1231">
+        <v>1.1529999971389771</v>
+      </c>
+      <c r="F1231">
+        <v>4089700</v>
+      </c>
+      <c r="G1231">
+        <v>40897</v>
+      </c>
+      <c r="H1231">
+        <f t="shared" si="144"/>
+        <v>1229</v>
+      </c>
+      <c r="I1231">
+        <f>SUM($F$3:F1231)/H1231</f>
+        <v>4019150.3301718878</v>
+      </c>
+      <c r="N1231">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1231">
+        <f t="shared" si="158"/>
+        <v>1.1000000238418579</v>
+      </c>
+      <c r="P1231">
+        <f t="shared" si="143"/>
+        <v>1.1586666504542034</v>
+      </c>
+      <c r="Q1231">
+        <f t="shared" si="132"/>
+        <v>1.1809761836415245</v>
+      </c>
+      <c r="R1231">
+        <f t="shared" si="133"/>
+        <v>-2.2309533187321096E-2</v>
+      </c>
+      <c r="S1231">
+        <f t="shared" si="134"/>
+        <v>2.5265306031622851E-2</v>
+      </c>
+      <c r="T1231">
+        <f t="shared" si="135"/>
+        <v>3.7897959047434275E-4</v>
+      </c>
+      <c r="U1231">
+        <f t="shared" si="136"/>
+        <v>-58.867373726901185</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1232" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B1232">
+        <v>1.156000018119812</v>
+      </c>
+      <c r="C1232">
+        <v>1.1640000343322754</v>
+      </c>
+      <c r="D1232">
+        <v>1.1529999971389771</v>
+      </c>
+      <c r="E1232">
+        <v>1.1579999923706055</v>
+      </c>
+      <c r="F1232">
+        <v>1158500</v>
+      </c>
+      <c r="G1232">
+        <v>11585</v>
+      </c>
+      <c r="H1232">
+        <f t="shared" si="144"/>
+        <v>1230</v>
+      </c>
+      <c r="I1232">
+        <f>SUM($F$3:F1232)/H1232</f>
+        <v>4016824.5981961382</v>
+      </c>
+      <c r="N1232">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1232">
+        <f t="shared" si="158"/>
+        <v>1.1000000238418579</v>
+      </c>
+      <c r="P1232">
+        <f t="shared" si="143"/>
+        <v>1.1583333412806194</v>
+      </c>
+      <c r="Q1232">
+        <f t="shared" si="132"/>
+        <v>1.1765238018262953</v>
+      </c>
+      <c r="R1232">
+        <f t="shared" si="133"/>
+        <v>-1.8190460545675968E-2</v>
+      </c>
+      <c r="S1232">
+        <f t="shared" si="134"/>
+        <v>2.4306118893785533E-2</v>
+      </c>
+      <c r="T1232">
+        <f t="shared" si="135"/>
+        <v>3.6459178340678296E-4</v>
+      </c>
+      <c r="U1232">
+        <f t="shared" si="136"/>
+        <v>-49.892678259785349</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1233" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B1233">
+        <v>1.1649999618530273</v>
+      </c>
+      <c r="C1233">
+        <v>1.1929999589920044</v>
+      </c>
+      <c r="D1233">
+        <v>1.1349999904632568</v>
+      </c>
+      <c r="E1233">
+        <v>1.1349999904632568</v>
+      </c>
+      <c r="F1233">
+        <v>558600</v>
+      </c>
+      <c r="G1233">
+        <v>5586</v>
+      </c>
+      <c r="H1233">
+        <f t="shared" si="144"/>
+        <v>1231</v>
+      </c>
+      <c r="I1233">
+        <f>SUM($F$3:F1233)/H1233</f>
+        <v>4014015.3174502435</v>
+      </c>
+      <c r="N1233">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1233">
+        <f t="shared" si="158"/>
+        <v>1.1000000238418579</v>
+      </c>
+      <c r="P1233">
+        <f t="shared" si="143"/>
+        <v>1.1543333133061726</v>
+      </c>
+      <c r="Q1233">
+        <f t="shared" si="132"/>
+        <v>1.1721428490820383</v>
+      </c>
+      <c r="R1233">
+        <f t="shared" si="133"/>
+        <v>-1.7809535775865637E-2</v>
+      </c>
+      <c r="S1233">
+        <f t="shared" si="134"/>
+        <v>2.3095235938117607E-2</v>
+      </c>
+      <c r="T1233">
+        <f t="shared" si="135"/>
+        <v>3.4642853907176409E-4</v>
+      </c>
+      <c r="U1233">
+        <f t="shared" si="136"/>
+        <v>-51.408974051575811</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1234" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B1234">
+        <v>1.1529999971389771</v>
+      </c>
+      <c r="C1234">
+        <v>1.1610000133514404</v>
+      </c>
+      <c r="D1234">
+        <v>1.1289999485015869</v>
+      </c>
+      <c r="E1234">
+        <v>1.1610000133514404</v>
+      </c>
+      <c r="F1234">
+        <v>5191200</v>
+      </c>
+      <c r="G1234">
+        <v>51912</v>
+      </c>
+      <c r="H1234">
+        <f t="shared" si="144"/>
+        <v>1232</v>
+      </c>
+      <c r="I1234">
+        <f>SUM($F$3:F1234)/H1234</f>
+        <v>4014970.8244977677</v>
+      </c>
+      <c r="N1234">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1234">
+        <f t="shared" si="158"/>
+        <v>1.1000000238418579</v>
+      </c>
+      <c r="P1234">
+        <f t="shared" si="143"/>
+        <v>1.150333325068156</v>
+      </c>
+      <c r="Q1234">
+        <f t="shared" si="132"/>
+        <v>1.1684761813708715</v>
+      </c>
+      <c r="R1234">
+        <f t="shared" si="133"/>
+        <v>-1.8142856302715504E-2</v>
+      </c>
+      <c r="S1234">
+        <f t="shared" si="134"/>
+        <v>2.2190471490224191E-2</v>
+      </c>
+      <c r="T1234">
+        <f t="shared" si="135"/>
+        <v>3.3285707235336287E-4</v>
+      </c>
+      <c r="U1234">
+        <f t="shared" si="136"/>
+        <v>-54.506446789434442</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1235" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B1235">
+        <v>1.1380000114440918</v>
+      </c>
+      <c r="C1235">
+        <v>1.1410000324249268</v>
+      </c>
+      <c r="D1235">
+        <v>1.1009999513626099</v>
+      </c>
+      <c r="E1235">
+        <v>1.1030000448226929</v>
+      </c>
+      <c r="F1235">
+        <v>2865200</v>
+      </c>
+      <c r="G1235">
+        <v>28652</v>
+      </c>
+      <c r="H1235">
+        <f t="shared" si="144"/>
+        <v>1233</v>
+      </c>
+      <c r="I1235">
+        <f>SUM($F$3:F1235)/H1235</f>
+        <v>4014038.3258566502</v>
+      </c>
+      <c r="N1235">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1235">
+        <f t="shared" si="158"/>
+        <v>1.1000000238418579</v>
+      </c>
+      <c r="P1235">
+        <f t="shared" si="143"/>
+        <v>1.1150000095367432</v>
+      </c>
+      <c r="Q1235">
+        <f t="shared" si="132"/>
+        <v>1.1629761854807534</v>
+      </c>
+      <c r="R1235">
+        <f t="shared" si="133"/>
+        <v>-4.7976175944010269E-2</v>
+      </c>
+      <c r="S1235">
+        <f t="shared" si="134"/>
+        <v>2.3544215020679254E-2</v>
+      </c>
+      <c r="T1235">
+        <f t="shared" si="135"/>
+        <v>3.5316322531018878E-4</v>
+      </c>
+      <c r="U1235">
+        <f t="shared" si="136"/>
+        <v>-135.84703192658876</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1236" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B1236">
+        <v>1.1119999885559082</v>
+      </c>
+      <c r="C1236">
+        <v>1.1269999742507935</v>
+      </c>
+      <c r="D1236">
+        <v>1.0880000591278076</v>
+      </c>
+      <c r="E1236">
+        <v>1.1200000047683716</v>
+      </c>
+      <c r="F1236">
+        <v>3663200</v>
+      </c>
+      <c r="G1236">
+        <v>36632</v>
+      </c>
+      <c r="H1236">
+        <f t="shared" si="144"/>
+        <v>1234</v>
+      </c>
+      <c r="I1236">
+        <f>SUM($F$3:F1236)/H1236</f>
+        <v>4013754.0160301863</v>
+      </c>
+      <c r="N1236">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1236">
+        <f t="shared" si="158"/>
+        <v>1.0880000591278076</v>
+      </c>
+      <c r="P1236">
+        <f t="shared" si="143"/>
+        <v>1.1116666793823242</v>
+      </c>
+      <c r="Q1236">
+        <f t="shared" si="132"/>
+        <v>1.1559047585441953</v>
+      </c>
+      <c r="R1236">
+        <f t="shared" si="133"/>
+        <v>-4.4238079161871058E-2</v>
+      </c>
+      <c r="S1236">
+        <f t="shared" si="134"/>
+        <v>2.2523806208655954E-2</v>
+      </c>
+      <c r="T1236">
+        <f t="shared" si="135"/>
+        <v>3.3785709312983929E-4</v>
+      </c>
+      <c r="U1236">
+        <f t="shared" si="136"/>
+        <v>-130.93725146350636</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1237" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B1237">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="C1237">
+        <v>1.1109999418258667</v>
+      </c>
+      <c r="D1237">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="E1237">
+        <v>1.090999960899353</v>
+      </c>
+      <c r="F1237">
+        <v>2797904</v>
+      </c>
+      <c r="G1237">
+        <v>27979.0390625</v>
+      </c>
+      <c r="H1237">
+        <f t="shared" si="144"/>
+        <v>1235</v>
+      </c>
+      <c r="I1237">
+        <f>SUM($F$3:F1237)/H1237</f>
+        <v>4012769.5220900811</v>
+      </c>
+      <c r="N1237">
+        <f t="shared" si="157"/>
+        <v>1.281999945640564</v>
+      </c>
+      <c r="O1237">
+        <f t="shared" si="158"/>
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="P1237">
+        <f t="shared" si="143"/>
+        <v>1.0923333168029785</v>
+      </c>
+      <c r="Q1237">
+        <f t="shared" si="132"/>
+        <v>1.1480238068671453</v>
+      </c>
+      <c r="R1237">
+        <f t="shared" si="133"/>
+        <v>-5.569049006416682E-2</v>
+      </c>
+      <c r="S1237">
+        <f t="shared" si="134"/>
+        <v>2.4350338647154746E-2</v>
+      </c>
+      <c r="T1237">
+        <f t="shared" si="135"/>
+        <v>3.6525507970732119E-4</v>
+      </c>
+      <c r="U1237">
+        <f t="shared" si="136"/>
+        <v>-152.47013158254117</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1237"/>
+  <dimension ref="A1:U1238"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -4479,7 +4479,7 @@
         <v>-133.95931142410072</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>44462</v>
       </c>
@@ -4509,6 +4509,12 @@
         <f>SUM($F$3:F64)/H64</f>
         <v>17357409.790322579</v>
       </c>
+      <c r="K64" s="2">
+        <v>46265</v>
+      </c>
+      <c r="L64" s="2">
+        <v>46237</v>
+      </c>
       <c r="N64">
         <f t="shared" si="11"/>
         <v>0.98799999999999999</v>
@@ -65821,23 +65827,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1237" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1238" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1237" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1238" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1237" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1238" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1237" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1238" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1237" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1238" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68967,7 +68973,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1237" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1238" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69077,7 +69083,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1237" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1238" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -77086,11 +77092,11 @@
         <v>4025192.6272909804</v>
       </c>
       <c r="N1216">
-        <f t="shared" ref="N1216:N1237" si="157">IF(A1216&lt;&gt;$K$63,MAX(N1215,VLOOKUP(A1216,A:C,3)),)</f>
+        <f t="shared" ref="N1216:N1238" si="157">IF(A1216&lt;&gt;$K$63,MAX(N1215,VLOOKUP(A1216,A:C,3)),)</f>
         <v>1.281999945640564</v>
       </c>
       <c r="O1216">
-        <f t="shared" ref="O1216:O1237" si="158">IF(A1216&lt;&gt;$K$63,MIN(O1215,VLOOKUP(A1216,A:D,4)),)</f>
+        <f t="shared" ref="O1216:O1238" si="158">IF(A1216&lt;&gt;$K$63,MIN(O1215,VLOOKUP(A1216,A:D,4)),)</f>
         <v>1.253000020980835</v>
       </c>
       <c r="P1216">
@@ -78439,6 +78445,69 @@
       <c r="U1237">
         <f t="shared" si="136"/>
         <v>-152.47013158254117</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1238" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B1238">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="C1238">
+        <v>1.1289999485015869</v>
+      </c>
+      <c r="D1238">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="E1238">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="F1238">
+        <v>4485200</v>
+      </c>
+      <c r="G1238">
+        <v>44852</v>
+      </c>
+      <c r="H1238">
+        <f t="shared" si="144"/>
+        <v>1236</v>
+      </c>
+      <c r="I1238">
+        <f>SUM($F$3:F1238)/H1238</f>
+        <v>4013151.7473958335</v>
+      </c>
+      <c r="N1238">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="O1238">
+        <f t="shared" si="158"/>
+        <v>0</v>
+      </c>
+      <c r="P1238">
+        <f t="shared" si="143"/>
+        <v>1.1116666396458943</v>
+      </c>
+      <c r="Q1238">
+        <f t="shared" si="132"/>
+        <v>1.1438809491339186</v>
+      </c>
+      <c r="R1238">
+        <f t="shared" si="133"/>
+        <v>-3.2214309488024284E-2</v>
+      </c>
+      <c r="S1238">
+        <f t="shared" si="134"/>
+        <v>2.5993198764567467E-2</v>
+      </c>
+      <c r="T1238">
+        <f t="shared" si="135"/>
+        <v>3.8989798146851198E-4</v>
+      </c>
+      <c r="U1238">
+        <f t="shared" si="136"/>
+        <v>-82.62240642203966</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1238"/>
+  <dimension ref="A1:U1258"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -65827,23 +65827,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1238" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1258" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1238" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1258" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1238" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1258" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1238" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1258" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1238" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1258" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68973,7 +68973,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1238" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1258" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69083,7 +69083,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1238" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1258" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -77092,11 +77092,11 @@
         <v>4025192.6272909804</v>
       </c>
       <c r="N1216">
-        <f t="shared" ref="N1216:N1238" si="157">IF(A1216&lt;&gt;$K$63,MAX(N1215,VLOOKUP(A1216,A:C,3)),)</f>
+        <f t="shared" ref="N1216:N1237" si="157">IF(A1216&lt;&gt;$K$63,MAX(N1215,VLOOKUP(A1216,A:C,3)),)</f>
         <v>1.281999945640564</v>
       </c>
       <c r="O1216">
-        <f t="shared" ref="O1216:O1238" si="158">IF(A1216&lt;&gt;$K$63,MIN(O1215,VLOOKUP(A1216,A:D,4)),)</f>
+        <f t="shared" ref="O1216:O1237" si="158">IF(A1216&lt;&gt;$K$63,MIN(O1215,VLOOKUP(A1216,A:D,4)),)</f>
         <v>1.253000020980835</v>
       </c>
       <c r="P1216">
@@ -78478,12 +78478,12 @@
         <v>4013151.7473958335</v>
       </c>
       <c r="N1238">
-        <f t="shared" si="157"/>
-        <v>0</v>
+        <f>VLOOKUP(L64,A:C,3)</f>
+        <v>1.1039999723434448</v>
       </c>
       <c r="O1238">
-        <f t="shared" si="158"/>
-        <v>0</v>
+        <f>VLOOKUP(L64,A:D,4)</f>
+        <v>1.093000054359436</v>
       </c>
       <c r="P1238">
         <f t="shared" si="143"/>
@@ -78508,6 +78508,1266 @@
       <c r="U1238">
         <f t="shared" si="136"/>
         <v>-82.62240642203966</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1239" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B1239">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="C1239">
+        <v>1.1039999723434448</v>
+      </c>
+      <c r="D1239">
+        <v>1.093000054359436</v>
+      </c>
+      <c r="E1239">
+        <v>1.0950000286102295</v>
+      </c>
+      <c r="F1239">
+        <v>3069500</v>
+      </c>
+      <c r="G1239">
+        <v>30695</v>
+      </c>
+      <c r="H1239">
+        <f t="shared" si="144"/>
+        <v>1237</v>
+      </c>
+      <c r="I1239">
+        <f>SUM($F$3:F1239)/H1239</f>
+        <v>4012388.8923049718</v>
+      </c>
+      <c r="N1239">
+        <f t="shared" ref="N1239:N1258" si="159">IF(A1239&lt;&gt;$K$64,MAX(N1238,VLOOKUP(A1239,A:C,3)),)</f>
+        <v>1.1039999723434448</v>
+      </c>
+      <c r="O1239">
+        <f t="shared" ref="O1239:O1258" si="160">IF(A1239&lt;&gt;$K$64,MIN(O1238,VLOOKUP(A1239,A:D,4)),)</f>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1239">
+        <f t="shared" si="143"/>
+        <v>1.0973333517710369</v>
+      </c>
+      <c r="Q1239">
+        <f t="shared" si="132"/>
+        <v>1.1377142838069372</v>
+      </c>
+      <c r="R1239">
+        <f t="shared" si="133"/>
+        <v>-4.0380932035900319E-2</v>
+      </c>
+      <c r="S1239">
+        <f t="shared" si="134"/>
+        <v>2.647619020371212E-2</v>
+      </c>
+      <c r="T1239">
+        <f t="shared" si="135"/>
+        <v>3.9714285305568177E-4</v>
+      </c>
+      <c r="U1239">
+        <f t="shared" si="136"/>
+        <v>-101.67860689221234</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1240" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B1240">
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="C1240">
+        <v>1.1310000419616699</v>
+      </c>
+      <c r="D1240">
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="E1240">
+        <v>1.1299999952316284</v>
+      </c>
+      <c r="F1240">
+        <v>2787702</v>
+      </c>
+      <c r="G1240">
+        <v>27877.01953125</v>
+      </c>
+      <c r="H1240">
+        <f t="shared" si="144"/>
+        <v>1238</v>
+      </c>
+      <c r="I1240">
+        <f>SUM($F$3:F1240)/H1240</f>
+        <v>4011399.6460268577</v>
+      </c>
+      <c r="N1240">
+        <f t="shared" si="159"/>
+        <v>1.1310000419616699</v>
+      </c>
+      <c r="O1240">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1240">
+        <f t="shared" si="143"/>
+        <v>1.122000018755595</v>
+      </c>
+      <c r="Q1240">
+        <f t="shared" si="132"/>
+        <v>1.1323095219475883</v>
+      </c>
+      <c r="R1240">
+        <f t="shared" si="133"/>
+        <v>-1.0309503191993308E-2</v>
+      </c>
+      <c r="S1240">
+        <f t="shared" si="134"/>
+        <v>2.2544214514648036E-2</v>
+      </c>
+      <c r="T1240">
+        <f t="shared" si="135"/>
+        <v>3.381632177197205E-4</v>
+      </c>
+      <c r="U1240">
+        <f t="shared" si="136"/>
+        <v>-30.486766897688216</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1241" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B1241">
+        <v>1.1100000143051147</v>
+      </c>
+      <c r="C1241">
+        <v>1.1499999761581421</v>
+      </c>
+      <c r="D1241">
+        <v>1.1100000143051147</v>
+      </c>
+      <c r="E1241">
+        <v>1.1399999856948853</v>
+      </c>
+      <c r="F1241">
+        <v>5111500</v>
+      </c>
+      <c r="G1241">
+        <v>51115</v>
+      </c>
+      <c r="H1241">
+        <f t="shared" si="144"/>
+        <v>1239</v>
+      </c>
+      <c r="I1241">
+        <f>SUM($F$3:F1241)/H1241</f>
+        <v>4012287.53977502</v>
+      </c>
+      <c r="N1241">
+        <f t="shared" si="159"/>
+        <v>1.1499999761581421</v>
+      </c>
+      <c r="O1241">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1241">
+        <f t="shared" si="143"/>
+        <v>1.1333333253860474</v>
+      </c>
+      <c r="Q1241">
+        <f t="shared" si="132"/>
+        <v>1.1290952364603679</v>
+      </c>
+      <c r="R1241">
+        <f t="shared" si="133"/>
+        <v>4.2380889256794507E-3</v>
+      </c>
+      <c r="S1241">
+        <f t="shared" si="134"/>
+        <v>1.8870745386396152E-2</v>
+      </c>
+      <c r="T1241">
+        <f t="shared" si="135"/>
+        <v>2.8306118079594227E-4</v>
+      </c>
+      <c r="U1241">
+        <f t="shared" si="136"/>
+        <v>14.972342423508341</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1242" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B1242">
+        <v>1.1210000514984131</v>
+      </c>
+      <c r="C1242">
+        <v>1.1469999551773071</v>
+      </c>
+      <c r="D1242">
+        <v>1.1189999580383301</v>
+      </c>
+      <c r="E1242">
+        <v>1.1360000371932983</v>
+      </c>
+      <c r="F1242">
+        <v>4146200</v>
+      </c>
+      <c r="G1242">
+        <v>41462</v>
+      </c>
+      <c r="H1242">
+        <f t="shared" si="144"/>
+        <v>1240</v>
+      </c>
+      <c r="I1242">
+        <f>SUM($F$3:F1242)/H1242</f>
+        <v>4012395.5336945564</v>
+      </c>
+      <c r="N1242">
+        <f t="shared" si="159"/>
+        <v>1.1499999761581421</v>
+      </c>
+      <c r="O1242">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1242">
+        <f t="shared" si="143"/>
+        <v>1.1339999834696453</v>
+      </c>
+      <c r="Q1242">
+        <f t="shared" si="132"/>
+        <v>1.1294999974114555</v>
+      </c>
+      <c r="R1242">
+        <f t="shared" si="133"/>
+        <v>4.4999860581897977E-3</v>
+      </c>
+      <c r="S1242">
+        <f t="shared" si="134"/>
+        <v>1.9166662579491036E-2</v>
+      </c>
+      <c r="T1242">
+        <f t="shared" si="135"/>
+        <v>2.8749993869236552E-4</v>
+      </c>
+      <c r="U1242">
+        <f t="shared" si="136"/>
+        <v>15.652128757512301</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1243" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B1243">
+        <v>1.1419999599456787</v>
+      </c>
+      <c r="C1243">
+        <v>1.1540000438690186</v>
+      </c>
+      <c r="D1243">
+        <v>1.1349999904632568</v>
+      </c>
+      <c r="E1243">
+        <v>1.1440000534057617</v>
+      </c>
+      <c r="F1243">
+        <v>4438800</v>
+      </c>
+      <c r="G1243">
+        <v>44388</v>
+      </c>
+      <c r="H1243">
+        <f t="shared" si="144"/>
+        <v>1241</v>
+      </c>
+      <c r="I1243">
+        <f>SUM($F$3:F1243)/H1243</f>
+        <v>4012739.1311694197</v>
+      </c>
+      <c r="N1243">
+        <f t="shared" si="159"/>
+        <v>1.1540000438690186</v>
+      </c>
+      <c r="O1243">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1243">
+        <f t="shared" si="143"/>
+        <v>1.1443333625793457</v>
+      </c>
+      <c r="Q1243">
+        <f t="shared" si="132"/>
+        <v>1.1310714284578958</v>
+      </c>
+      <c r="R1243">
+        <f t="shared" si="133"/>
+        <v>1.3261934121449936E-2</v>
+      </c>
+      <c r="S1243">
+        <f t="shared" si="134"/>
+        <v>1.9489793550400543E-2</v>
+      </c>
+      <c r="T1243">
+        <f t="shared" si="135"/>
+        <v>2.9234690325600815E-4</v>
+      </c>
+      <c r="U1243">
+        <f t="shared" si="136"/>
+        <v>45.363689417419486</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1244" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B1244">
+        <v>1.1440000534057617</v>
+      </c>
+      <c r="C1244">
+        <v>1.1469999551773071</v>
+      </c>
+      <c r="D1244">
+        <v>1.128000020980835</v>
+      </c>
+      <c r="E1244">
+        <v>1.1430000066757202</v>
+      </c>
+      <c r="F1244">
+        <v>5046700</v>
+      </c>
+      <c r="G1244">
+        <v>50467</v>
+      </c>
+      <c r="H1244">
+        <f t="shared" si="144"/>
+        <v>1242</v>
+      </c>
+      <c r="I1244">
+        <f>SUM($F$3:F1244)/H1244</f>
+        <v>4013571.6278431965</v>
+      </c>
+      <c r="N1244">
+        <f t="shared" si="159"/>
+        <v>1.1540000438690186</v>
+      </c>
+      <c r="O1244">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1244">
+        <f t="shared" si="143"/>
+        <v>1.1393333276112874</v>
+      </c>
+      <c r="Q1244">
+        <f t="shared" si="132"/>
+        <v>1.130190474646432</v>
+      </c>
+      <c r="R1244">
+        <f t="shared" si="133"/>
+        <v>9.1428529648553969E-3</v>
+      </c>
+      <c r="S1244">
+        <f t="shared" si="134"/>
+        <v>1.8734690283431506E-2</v>
+      </c>
+      <c r="T1244">
+        <f t="shared" si="135"/>
+        <v>2.810203542514726E-4</v>
+      </c>
+      <c r="U1244">
+        <f t="shared" si="136"/>
+        <v>32.534486653852355</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1245" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B1245">
+        <v>1.1430000066757202</v>
+      </c>
+      <c r="C1245">
+        <v>1.1540000438690186</v>
+      </c>
+      <c r="D1245">
+        <v>1.1399999856948853</v>
+      </c>
+      <c r="E1245">
+        <v>1.1430000066757202</v>
+      </c>
+      <c r="F1245">
+        <v>3857400</v>
+      </c>
+      <c r="G1245">
+        <v>38574</v>
+      </c>
+      <c r="H1245">
+        <f t="shared" si="144"/>
+        <v>1243</v>
+      </c>
+      <c r="I1245">
+        <f>SUM($F$3:F1245)/H1245</f>
+        <v>4013445.9869519309</v>
+      </c>
+      <c r="N1245">
+        <f t="shared" si="159"/>
+        <v>1.1540000438690186</v>
+      </c>
+      <c r="O1245">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1245">
+        <f t="shared" si="143"/>
+        <v>1.1456666787465413</v>
+      </c>
+      <c r="Q1245">
+        <f t="shared" si="132"/>
+        <v>1.1292619052387418</v>
+      </c>
+      <c r="R1245">
+        <f t="shared" si="133"/>
+        <v>1.6404773507799453E-2</v>
+      </c>
+      <c r="S1245">
+        <f t="shared" si="134"/>
+        <v>1.793877364826852E-2</v>
+      </c>
+      <c r="T1245">
+        <f t="shared" si="135"/>
+        <v>2.690816047240278E-4</v>
+      </c>
+      <c r="U1245">
+        <f t="shared" si="136"/>
+        <v>60.965793349658057</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1246" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B1246">
+        <v>1.121999979019165</v>
+      </c>
+      <c r="C1246">
+        <v>1.1549999713897705</v>
+      </c>
+      <c r="D1246">
+        <v>1.121999979019165</v>
+      </c>
+      <c r="E1246">
+        <v>1.1510000228881836</v>
+      </c>
+      <c r="F1246">
+        <v>2439400</v>
+      </c>
+      <c r="G1246">
+        <v>24394</v>
+      </c>
+      <c r="H1246">
+        <f t="shared" si="144"/>
+        <v>1244</v>
+      </c>
+      <c r="I1246">
+        <f>SUM($F$3:F1246)/H1246</f>
+        <v>4012180.6766730305</v>
+      </c>
+      <c r="N1246">
+        <f t="shared" si="159"/>
+        <v>1.1549999713897705</v>
+      </c>
+      <c r="O1246">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1246">
+        <f t="shared" si="143"/>
+        <v>1.1426666577657063</v>
+      </c>
+      <c r="Q1246">
+        <f t="shared" si="132"/>
+        <v>1.1281428564162481</v>
+      </c>
+      <c r="R1246">
+        <f t="shared" si="133"/>
+        <v>1.4523801349458187E-2</v>
+      </c>
+      <c r="S1246">
+        <f t="shared" si="134"/>
+        <v>1.6979588943273831E-2</v>
+      </c>
+      <c r="T1246">
+        <f t="shared" si="135"/>
+        <v>2.5469383414910744E-4</v>
+      </c>
+      <c r="U1246">
+        <f t="shared" si="136"/>
+        <v>57.02455027221194</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1247" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B1247">
+        <v>1.1469999551773071</v>
+      </c>
+      <c r="C1247">
+        <v>1.1649999618530273</v>
+      </c>
+      <c r="D1247">
+        <v>1.1469999551773071</v>
+      </c>
+      <c r="E1247">
+        <v>1.1469999551773071</v>
+      </c>
+      <c r="F1247">
+        <v>2805100</v>
+      </c>
+      <c r="G1247">
+        <v>28051</v>
+      </c>
+      <c r="H1247">
+        <f t="shared" si="144"/>
+        <v>1245</v>
+      </c>
+      <c r="I1247">
+        <f>SUM($F$3:F1247)/H1247</f>
+        <v>4011211.1339608436</v>
+      </c>
+      <c r="N1247">
+        <f t="shared" si="159"/>
+        <v>1.1649999618530273</v>
+      </c>
+      <c r="O1247">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1247">
+        <f t="shared" si="143"/>
+        <v>1.1529999574025471</v>
+      </c>
+      <c r="Q1247">
+        <f t="shared" si="132"/>
+        <v>1.1280476167088465</v>
+      </c>
+      <c r="R1247">
+        <f t="shared" si="133"/>
+        <v>2.495234069370067E-2</v>
+      </c>
+      <c r="S1247">
+        <f t="shared" si="134"/>
+        <v>1.6897954908357962E-2</v>
+      </c>
+      <c r="T1247">
+        <f t="shared" si="135"/>
+        <v>2.5346932362536943E-4</v>
+      </c>
+      <c r="U1247">
+        <f t="shared" si="136"/>
+        <v>98.443236983503837</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1248" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B1248">
+        <v>1.1510000228881836</v>
+      </c>
+      <c r="C1248">
+        <v>1.1510000228881836</v>
+      </c>
+      <c r="D1248">
+        <v>1.1399999856948853</v>
+      </c>
+      <c r="E1248">
+        <v>1.1490000486373901</v>
+      </c>
+      <c r="F1248">
+        <v>3827400</v>
+      </c>
+      <c r="G1248">
+        <v>38274</v>
+      </c>
+      <c r="H1248">
+        <f t="shared" si="144"/>
+        <v>1246</v>
+      </c>
+      <c r="I1248">
+        <f>SUM($F$3:F1248)/H1248</f>
+        <v>4011063.6129865572</v>
+      </c>
+      <c r="N1248">
+        <f t="shared" si="159"/>
+        <v>1.1649999618530273</v>
+      </c>
+      <c r="O1248">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1248">
+        <f t="shared" si="143"/>
+        <v>1.1466666857401531</v>
+      </c>
+      <c r="Q1248">
+        <f t="shared" si="132"/>
+        <v>1.1277857138997034</v>
+      </c>
+      <c r="R1248">
+        <f t="shared" si="133"/>
+        <v>1.8880971840449678E-2</v>
+      </c>
+      <c r="S1248">
+        <f t="shared" si="134"/>
+        <v>1.6673466786235332E-2</v>
+      </c>
+      <c r="T1248">
+        <f t="shared" si="135"/>
+        <v>2.5010200179352999E-4</v>
+      </c>
+      <c r="U1248">
+        <f t="shared" si="136"/>
+        <v>75.49308564126062</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1249" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B1249">
+        <v>1.1529999971389771</v>
+      </c>
+      <c r="C1249">
+        <v>1.1749999523162842</v>
+      </c>
+      <c r="D1249">
+        <v>1.1469999551773071</v>
+      </c>
+      <c r="E1249">
+        <v>1.1740000247955322</v>
+      </c>
+      <c r="F1249">
+        <v>3545900</v>
+      </c>
+      <c r="G1249">
+        <v>35459</v>
+      </c>
+      <c r="H1249">
+        <f t="shared" si="144"/>
+        <v>1247</v>
+      </c>
+      <c r="I1249">
+        <f>SUM($F$3:F1249)/H1249</f>
+        <v>4010690.5868334002</v>
+      </c>
+      <c r="N1249">
+        <f t="shared" si="159"/>
+        <v>1.1749999523162842</v>
+      </c>
+      <c r="O1249">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1249">
+        <f t="shared" si="143"/>
+        <v>1.1653333107630413</v>
+      </c>
+      <c r="Q1249">
+        <f t="shared" si="132"/>
+        <v>1.1313809497015819</v>
+      </c>
+      <c r="R1249">
+        <f t="shared" si="133"/>
+        <v>3.395236106145938E-2</v>
+      </c>
+      <c r="S1249">
+        <f t="shared" si="134"/>
+        <v>1.7414963164297026E-2</v>
+      </c>
+      <c r="T1249">
+        <f t="shared" si="135"/>
+        <v>2.6122444746445536E-4</v>
+      </c>
+      <c r="U1249">
+        <f t="shared" si="136"/>
+        <v>129.97390325068736</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1250" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B1250">
+        <v>1.1740000247955322</v>
+      </c>
+      <c r="C1250">
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="D1250">
+        <v>1.1579999923706055</v>
+      </c>
+      <c r="E1250">
+        <v>1.1679999828338623</v>
+      </c>
+      <c r="F1250">
+        <v>3209400</v>
+      </c>
+      <c r="G1250">
+        <v>32094</v>
+      </c>
+      <c r="H1250">
+        <f t="shared" si="144"/>
+        <v>1248</v>
+      </c>
+      <c r="I1250">
+        <f>SUM($F$3:F1250)/H1250</f>
+        <v>4010048.5270683095</v>
+      </c>
+      <c r="N1250">
+        <f t="shared" si="159"/>
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="O1250">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1250">
+        <f t="shared" si="143"/>
+        <v>1.1673333247502644</v>
+      </c>
+      <c r="Q1250">
+        <f t="shared" si="132"/>
+        <v>1.1353571386564347</v>
+      </c>
+      <c r="R1250">
+        <f t="shared" si="133"/>
+        <v>3.1976186093829684E-2</v>
+      </c>
+      <c r="S1250">
+        <f t="shared" si="134"/>
+        <v>1.7353742301058555E-2</v>
+      </c>
+      <c r="T1250">
+        <f t="shared" si="135"/>
+        <v>2.6030613451587833E-4</v>
+      </c>
+      <c r="U1250">
+        <f t="shared" si="136"/>
+        <v>122.8406935291768</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1251" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B1251">
+        <v>1.1449999809265137</v>
+      </c>
+      <c r="C1251">
+        <v>1.1449999809265137</v>
+      </c>
+      <c r="D1251">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="E1251">
+        <v>1.1180000305175781</v>
+      </c>
+      <c r="F1251">
+        <v>4864400</v>
+      </c>
+      <c r="G1251">
+        <v>48644</v>
+      </c>
+      <c r="H1251">
+        <f t="shared" si="144"/>
+        <v>1249</v>
+      </c>
+      <c r="I1251">
+        <f>SUM($F$3:F1251)/H1251</f>
+        <v>4010732.5554693756</v>
+      </c>
+      <c r="N1251">
+        <f t="shared" si="159"/>
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="O1251">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1251">
+        <f t="shared" si="143"/>
+        <v>1.1256666580835979</v>
+      </c>
+      <c r="Q1251">
+        <f t="shared" si="132"/>
+        <v>1.1377380916050501</v>
+      </c>
+      <c r="R1251">
+        <f t="shared" si="133"/>
+        <v>-1.2071433521452235E-2</v>
+      </c>
+      <c r="S1251">
+        <f t="shared" si="134"/>
+        <v>1.4632653216926401E-2</v>
+      </c>
+      <c r="T1251">
+        <f t="shared" si="135"/>
+        <v>2.1948979825389602E-4</v>
+      </c>
+      <c r="U1251">
+        <f t="shared" si="136"/>
+        <v>-54.997697466961718</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1252" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B1252">
+        <v>1.1260000467300415</v>
+      </c>
+      <c r="C1252">
+        <v>1.1310000419616699</v>
+      </c>
+      <c r="D1252">
+        <v>1.1150000095367432</v>
+      </c>
+      <c r="E1252">
+        <v>1.1210000514984131</v>
+      </c>
+      <c r="F1252">
+        <v>4431700</v>
+      </c>
+      <c r="G1252">
+        <v>44317</v>
+      </c>
+      <c r="H1252">
+        <f t="shared" si="144"/>
+        <v>1250</v>
+      </c>
+      <c r="I1252">
+        <f>SUM($F$3:F1252)/H1252</f>
+        <v>4011069.3294250001</v>
+      </c>
+      <c r="N1252">
+        <f t="shared" si="159"/>
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="O1252">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1252">
+        <f t="shared" si="143"/>
+        <v>1.1223333676656086</v>
+      </c>
+      <c r="Q1252">
+        <f t="shared" si="132"/>
+        <v>1.1385000007493156</v>
+      </c>
+      <c r="R1252">
+        <f t="shared" si="133"/>
+        <v>-1.6166633083706916E-2</v>
+      </c>
+      <c r="S1252">
+        <f t="shared" si="134"/>
+        <v>1.3761899909194599E-2</v>
+      </c>
+      <c r="T1252">
+        <f t="shared" si="135"/>
+        <v>2.0642849863791897E-4</v>
+      </c>
+      <c r="U1252">
+        <f t="shared" si="136"/>
+        <v>-78.315897225332321</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1253" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B1253">
+        <v>1.1200000047683716</v>
+      </c>
+      <c r="C1253">
+        <v>1.1399999856948853</v>
+      </c>
+      <c r="D1253">
+        <v>1.1200000047683716</v>
+      </c>
+      <c r="E1253">
+        <v>1.1369999647140503</v>
+      </c>
+      <c r="F1253">
+        <v>3039800</v>
+      </c>
+      <c r="G1253">
+        <v>30398</v>
+      </c>
+      <c r="H1253">
+        <f t="shared" si="144"/>
+        <v>1251</v>
+      </c>
+      <c r="I1253">
+        <f>SUM($F$3:F1253)/H1253</f>
+        <v>4010292.9350769385</v>
+      </c>
+      <c r="N1253">
+        <f t="shared" si="159"/>
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="O1253">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1253">
+        <f t="shared" si="143"/>
+        <v>1.1323333183924358</v>
+      </c>
+      <c r="Q1253">
+        <f t="shared" si="132"/>
+        <v>1.1409999983651296</v>
+      </c>
+      <c r="R1253">
+        <f t="shared" si="133"/>
+        <v>-8.6666799726937693E-3</v>
+      </c>
+      <c r="S1253">
+        <f t="shared" si="134"/>
+        <v>1.1142855598812991E-2</v>
+      </c>
+      <c r="T1253">
+        <f t="shared" si="135"/>
+        <v>1.6714283398219486E-4</v>
+      </c>
+      <c r="U1253">
+        <f t="shared" si="136"/>
+        <v>-51.851938645583814</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1254" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B1254">
+        <v>1.1330000162124634</v>
+      </c>
+      <c r="C1254">
+        <v>1.1339999437332153</v>
+      </c>
+      <c r="D1254">
+        <v>1.1009999513626099</v>
+      </c>
+      <c r="E1254">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="F1254">
+        <v>4669300</v>
+      </c>
+      <c r="G1254">
+        <v>46693</v>
+      </c>
+      <c r="H1254">
+        <f t="shared" si="144"/>
+        <v>1252</v>
+      </c>
+      <c r="I1254">
+        <f>SUM($F$3:F1254)/H1254</f>
+        <v>4010819.2985473243</v>
+      </c>
+      <c r="N1254">
+        <f t="shared" si="159"/>
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="O1254">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1254">
+        <f t="shared" si="143"/>
+        <v>1.116333285967509</v>
+      </c>
+      <c r="Q1254">
+        <f t="shared" si="132"/>
+        <v>1.1405952317374093</v>
+      </c>
+      <c r="R1254">
+        <f t="shared" si="133"/>
+        <v>-2.4261945769900262E-2</v>
+      </c>
+      <c r="S1254">
+        <f t="shared" si="134"/>
+        <v>1.1547622226533414E-2</v>
+      </c>
+      <c r="T1254">
+        <f t="shared" si="135"/>
+        <v>1.7321433339800119E-4</v>
+      </c>
+      <c r="U1254">
+        <f t="shared" si="136"/>
+        <v>-140.0689267103125</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1255" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B1255">
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="C1255">
+        <v>1.1130000352859497</v>
+      </c>
+      <c r="D1255">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="E1255">
+        <v>1.1080000400543213</v>
+      </c>
+      <c r="F1255">
+        <v>2839602</v>
+      </c>
+      <c r="G1255">
+        <v>28396.01953125</v>
+      </c>
+      <c r="H1255">
+        <f t="shared" si="144"/>
+        <v>1253</v>
+      </c>
+      <c r="I1255">
+        <f>SUM($F$3:F1255)/H1255</f>
+        <v>4009884.5680616521</v>
+      </c>
+      <c r="N1255">
+        <f t="shared" si="159"/>
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="O1255">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1255">
+        <f t="shared" si="143"/>
+        <v>1.1066666841506958</v>
+      </c>
+      <c r="Q1255">
+        <f t="shared" si="132"/>
+        <v>1.1386904716491697</v>
+      </c>
+      <c r="R1255">
+        <f t="shared" si="133"/>
+        <v>-3.2023787498473899E-2</v>
+      </c>
+      <c r="S1255">
+        <f t="shared" si="134"/>
+        <v>1.354421888078962E-2</v>
+      </c>
+      <c r="T1255">
+        <f t="shared" si="135"/>
+        <v>2.031632832118443E-4</v>
+      </c>
+      <c r="U1255">
+        <f t="shared" si="136"/>
+        <v>-157.62586128853687</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1256" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B1256">
+        <v>1.1059999465942383</v>
+      </c>
+      <c r="C1256">
+        <v>1.1230000257492065</v>
+      </c>
+      <c r="D1256">
+        <v>1.1059999465942383</v>
+      </c>
+      <c r="E1256">
+        <v>1.1150000095367432</v>
+      </c>
+      <c r="F1256">
+        <v>1662702</v>
+      </c>
+      <c r="G1256">
+        <v>16627.01953125</v>
+      </c>
+      <c r="H1256">
+        <f t="shared" si="144"/>
+        <v>1254</v>
+      </c>
+      <c r="I1256">
+        <f>SUM($F$3:F1256)/H1256</f>
+        <v>4008012.8116277913</v>
+      </c>
+      <c r="N1256">
+        <f t="shared" si="159"/>
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="O1256">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1256">
+        <f t="shared" si="143"/>
+        <v>1.1146666606267293</v>
+      </c>
+      <c r="Q1256">
+        <f t="shared" si="132"/>
+        <v>1.1373095200175329</v>
+      </c>
+      <c r="R1256">
+        <f t="shared" si="133"/>
+        <v>-2.2642859390803682E-2</v>
+      </c>
+      <c r="S1256">
+        <f t="shared" si="134"/>
+        <v>1.5122449316946016E-2</v>
+      </c>
+      <c r="T1256">
+        <f t="shared" si="135"/>
+        <v>2.2683673975419023E-4</v>
+      </c>
+      <c r="U1256">
+        <f t="shared" si="136"/>
+        <v>-99.820070661130245</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1257" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B1257">
+        <v>1.1169999837875366</v>
+      </c>
+      <c r="C1257">
+        <v>1.125</v>
+      </c>
+      <c r="D1257">
+        <v>1.1130000352859497</v>
+      </c>
+      <c r="E1257">
+        <v>1.1230000257492065</v>
+      </c>
+      <c r="F1257">
+        <v>873400</v>
+      </c>
+      <c r="G1257">
+        <v>8734</v>
+      </c>
+      <c r="H1257">
+        <f t="shared" si="144"/>
+        <v>1255</v>
+      </c>
+      <c r="I1257">
+        <f>SUM($F$3:F1257)/H1257</f>
+        <v>4005515.1121762949</v>
+      </c>
+      <c r="N1257">
+        <f t="shared" si="159"/>
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="O1257">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1257">
+        <f t="shared" si="143"/>
+        <v>1.1203333536783855</v>
+      </c>
+      <c r="Q1257">
+        <f t="shared" si="132"/>
+        <v>1.1355952336674644</v>
+      </c>
+      <c r="R1257">
+        <f t="shared" si="133"/>
+        <v>-1.5261879989078908E-2</v>
+      </c>
+      <c r="S1257">
+        <f t="shared" si="134"/>
+        <v>1.5833329586755634E-2</v>
+      </c>
+      <c r="T1257">
+        <f t="shared" si="135"/>
+        <v>2.3749994380133449E-4</v>
+      </c>
+      <c r="U1257">
+        <f t="shared" si="136"/>
+        <v>-64.260562528154807</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1258" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B1258">
+        <v>1.1239999532699585</v>
+      </c>
+      <c r="C1258">
+        <v>1.1349999904632568</v>
+      </c>
+      <c r="D1258">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="E1258">
+        <v>1.1160000562667847</v>
+      </c>
+      <c r="F1258">
+        <v>1319000</v>
+      </c>
+      <c r="G1258">
+        <v>13190</v>
+      </c>
+      <c r="H1258">
+        <f t="shared" si="144"/>
+        <v>1256</v>
+      </c>
+      <c r="I1258">
+        <f>SUM($F$3:F1258)/H1258</f>
+        <v>4003376.1670232881</v>
+      </c>
+      <c r="N1258">
+        <f t="shared" si="159"/>
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="O1258">
+        <f t="shared" si="160"/>
+        <v>1.093000054359436</v>
+      </c>
+      <c r="P1258">
+        <f t="shared" si="143"/>
+        <v>1.1216666698455811</v>
+      </c>
+      <c r="Q1258">
+        <f t="shared" si="132"/>
+        <v>1.1343333295413427</v>
+      </c>
+      <c r="R1258">
+        <f t="shared" si="133"/>
+        <v>-1.266665969576164E-2</v>
+      </c>
+      <c r="S1258">
+        <f t="shared" si="134"/>
+        <v>1.6380948274313991E-2</v>
+      </c>
+      <c r="T1258">
+        <f t="shared" si="135"/>
+        <v>2.4571422411470988E-4</v>
+      </c>
+      <c r="U1258">
+        <f t="shared" si="136"/>
+        <v>-51.550372150406332</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1258"/>
+  <dimension ref="A1:U1259"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -4548,7 +4548,7 @@
         <v>-78.113440197288668</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>44463</v>
       </c>
@@ -4578,6 +4578,12 @@
         <f>SUM($F$3:F65)/H65</f>
         <v>17115726.222222224</v>
       </c>
+      <c r="K65" s="2">
+        <v>46295</v>
+      </c>
+      <c r="L65" s="2">
+        <v>46266</v>
+      </c>
       <c r="N65">
         <f t="shared" si="11"/>
         <v>0.98799999999999999</v>
@@ -65827,23 +65833,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1258" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1259" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1258" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1259" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1258" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1259" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1258" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1259" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1258" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1259" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68973,7 +68979,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1258" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1259" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69083,7 +69089,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1258" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1259" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -78541,11 +78547,11 @@
         <v>4012388.8923049718</v>
       </c>
       <c r="N1239">
-        <f t="shared" ref="N1239:N1258" si="159">IF(A1239&lt;&gt;$K$64,MAX(N1238,VLOOKUP(A1239,A:C,3)),)</f>
+        <f t="shared" ref="N1239:N1259" si="159">IF(A1239&lt;&gt;$K$64,MAX(N1238,VLOOKUP(A1239,A:C,3)),)</f>
         <v>1.1039999723434448</v>
       </c>
       <c r="O1239">
-        <f t="shared" ref="O1239:O1258" si="160">IF(A1239&lt;&gt;$K$64,MIN(O1238,VLOOKUP(A1239,A:D,4)),)</f>
+        <f t="shared" ref="O1239:O1259" si="160">IF(A1239&lt;&gt;$K$64,MIN(O1238,VLOOKUP(A1239,A:D,4)),)</f>
         <v>1.093000054359436</v>
       </c>
       <c r="P1239">
@@ -79768,6 +79774,69 @@
       <c r="U1258">
         <f t="shared" si="136"/>
         <v>-51.550372150406332</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1259" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B1259">
+        <v>1.1100000143051147</v>
+      </c>
+      <c r="C1259">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="D1259">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="E1259">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="F1259">
+        <v>1687200</v>
+      </c>
+      <c r="G1259">
+        <v>16872</v>
+      </c>
+      <c r="H1259">
+        <f t="shared" si="144"/>
+        <v>1257</v>
+      </c>
+      <c r="I1259">
+        <f>SUM($F$3:F1259)/H1259</f>
+        <v>4001533.5447742641</v>
+      </c>
+      <c r="N1259">
+        <f t="shared" si="159"/>
+        <v>0</v>
+      </c>
+      <c r="O1259">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="P1259">
+        <f t="shared" si="143"/>
+        <v>1.1089999675750732</v>
+      </c>
+      <c r="Q1259">
+        <f t="shared" si="132"/>
+        <v>1.1317142787433805</v>
+      </c>
+      <c r="R1259">
+        <f t="shared" si="133"/>
+        <v>-2.2714311168307244E-2</v>
+      </c>
+      <c r="S1259">
+        <f t="shared" si="134"/>
+        <v>1.6721083193409179E-2</v>
+      </c>
+      <c r="T1259">
+        <f t="shared" si="135"/>
+        <v>2.5081624790113767E-4</v>
+      </c>
+      <c r="U1259">
+        <f t="shared" si="136"/>
+        <v>-90.561561933820059</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1259"/>
+  <dimension ref="A1:U1279"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -65833,23 +65833,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1259" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1279" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1259" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1279" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1259" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1279" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1259" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1279" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1259" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1279" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68979,7 +68979,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1259" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1279" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69089,7 +69089,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1259" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1279" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -78547,11 +78547,11 @@
         <v>4012388.8923049718</v>
       </c>
       <c r="N1239">
-        <f t="shared" ref="N1239:N1259" si="159">IF(A1239&lt;&gt;$K$64,MAX(N1238,VLOOKUP(A1239,A:C,3)),)</f>
+        <f t="shared" ref="N1239:N1258" si="159">IF(A1239&lt;&gt;$K$64,MAX(N1238,VLOOKUP(A1239,A:C,3)),)</f>
         <v>1.1039999723434448</v>
       </c>
       <c r="O1239">
-        <f t="shared" ref="O1239:O1259" si="160">IF(A1239&lt;&gt;$K$64,MIN(O1238,VLOOKUP(A1239,A:D,4)),)</f>
+        <f t="shared" ref="O1239:O1258" si="160">IF(A1239&lt;&gt;$K$64,MIN(O1238,VLOOKUP(A1239,A:D,4)),)</f>
         <v>1.093000054359436</v>
       </c>
       <c r="P1239">
@@ -79807,12 +79807,12 @@
         <v>4001533.5447742641</v>
       </c>
       <c r="N1259">
-        <f t="shared" si="159"/>
-        <v>0</v>
+        <f>VLOOKUP(L65,A:C,3)</f>
+        <v>1.128000020980835</v>
       </c>
       <c r="O1259">
-        <f t="shared" si="160"/>
-        <v>0</v>
+        <f>VLOOKUP(L65,A:D,4)</f>
+        <v>1.0989999771118164</v>
       </c>
       <c r="P1259">
         <f t="shared" si="143"/>
@@ -79837,6 +79837,1266 @@
       <c r="U1259">
         <f t="shared" si="136"/>
         <v>-90.561561933820059</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1260" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B1260">
+        <v>1.1100000143051147</v>
+      </c>
+      <c r="C1260">
+        <v>1.128000020980835</v>
+      </c>
+      <c r="D1260">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="E1260">
+        <v>1.1080000400543213</v>
+      </c>
+      <c r="F1260">
+        <v>1161700</v>
+      </c>
+      <c r="G1260">
+        <v>11617</v>
+      </c>
+      <c r="H1260">
+        <f t="shared" si="144"/>
+        <v>1258</v>
+      </c>
+      <c r="I1260">
+        <f>SUM($F$3:F1260)/H1260</f>
+        <v>3999276.1254222975</v>
+      </c>
+      <c r="N1260">
+        <f t="shared" ref="N1260:N1279" si="161">IF(A1260&lt;&gt;$K$65,MAX(N1259,VLOOKUP(A1260,A:C,3)),)</f>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1260">
+        <f t="shared" ref="O1260:O1279" si="162">IF(A1260&lt;&gt;$K$65,MIN(O1259,VLOOKUP(A1260,A:D,4)),)</f>
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="P1260">
+        <f t="shared" si="143"/>
+        <v>1.1116666793823242</v>
+      </c>
+      <c r="Q1260">
+        <f t="shared" si="132"/>
+        <v>1.129499994573139</v>
+      </c>
+      <c r="R1260">
+        <f t="shared" si="133"/>
+        <v>-1.7833315190814769E-2</v>
+      </c>
+      <c r="S1260">
+        <f t="shared" si="134"/>
+        <v>1.6738089168963782E-2</v>
+      </c>
+      <c r="T1260">
+        <f t="shared" si="135"/>
+        <v>2.5107133753445672E-4</v>
+      </c>
+      <c r="U1260">
+        <f t="shared" si="136"/>
+        <v>-71.028877154754255</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1261" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B1261">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="C1261">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="D1261">
+        <v>1.0850000381469727</v>
+      </c>
+      <c r="E1261">
+        <v>1.0859999656677246</v>
+      </c>
+      <c r="F1261">
+        <v>861200</v>
+      </c>
+      <c r="G1261">
+        <v>8612</v>
+      </c>
+      <c r="H1261">
+        <f t="shared" si="144"/>
+        <v>1259</v>
+      </c>
+      <c r="I1261">
+        <f>SUM($F$3:F1261)/H1261</f>
+        <v>3996783.610628475</v>
+      </c>
+      <c r="N1261">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1261">
+        <f t="shared" si="162"/>
+        <v>1.0850000381469727</v>
+      </c>
+      <c r="P1261">
+        <f t="shared" si="143"/>
+        <v>1.0899999936421711</v>
+      </c>
+      <c r="Q1261">
+        <f t="shared" si="132"/>
+        <v>1.1249999971616835</v>
+      </c>
+      <c r="R1261">
+        <f t="shared" si="133"/>
+        <v>-3.5000003519512379E-2</v>
+      </c>
+      <c r="S1261">
+        <f t="shared" si="134"/>
+        <v>1.6047615988724902E-2</v>
+      </c>
+      <c r="T1261">
+        <f t="shared" si="135"/>
+        <v>2.4071423983087353E-4</v>
+      </c>
+      <c r="U1261">
+        <f t="shared" si="136"/>
+        <v>-145.40063580826575</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1262" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B1262">
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="C1262">
+        <v>1.0959999561309814</v>
+      </c>
+      <c r="D1262">
+        <v>1.0809999704360962</v>
+      </c>
+      <c r="E1262">
+        <v>1.0859999656677246</v>
+      </c>
+      <c r="F1262">
+        <v>3171800</v>
+      </c>
+      <c r="G1262">
+        <v>31718</v>
+      </c>
+      <c r="H1262">
+        <f t="shared" si="144"/>
+        <v>1260</v>
+      </c>
+      <c r="I1262">
+        <f>SUM($F$3:F1262)/H1262</f>
+        <v>3996128.8617311507</v>
+      </c>
+      <c r="N1262">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1262">
+        <f t="shared" si="162"/>
+        <v>1.0809999704360962</v>
+      </c>
+      <c r="P1262">
+        <f t="shared" si="143"/>
+        <v>1.0876666307449341</v>
+      </c>
+      <c r="Q1262">
+        <f t="shared" si="132"/>
+        <v>1.1207857075191681</v>
+      </c>
+      <c r="R1262">
+        <f t="shared" si="133"/>
+        <v>-3.311907677423398E-2</v>
+      </c>
+      <c r="S1262">
+        <f t="shared" si="134"/>
+        <v>1.5707486340788779E-2</v>
+      </c>
+      <c r="T1262">
+        <f t="shared" si="135"/>
+        <v>2.3561229511183168E-4</v>
+      </c>
+      <c r="U1262">
+        <f t="shared" si="136"/>
+        <v>-140.56599532937892</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1263" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B1263">
+        <v>1.0900000333786011</v>
+      </c>
+      <c r="C1263">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="D1263">
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="E1263">
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="F1263">
+        <v>2225200</v>
+      </c>
+      <c r="G1263">
+        <v>22252</v>
+      </c>
+      <c r="H1263">
+        <f t="shared" si="144"/>
+        <v>1261</v>
+      </c>
+      <c r="I1263">
+        <f>SUM($F$3:F1263)/H1263</f>
+        <v>3994724.4772254163</v>
+      </c>
+      <c r="N1263">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1263">
+        <f t="shared" si="162"/>
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="P1263">
+        <f t="shared" si="143"/>
+        <v>1.0853333473205566</v>
+      </c>
+      <c r="Q1263">
+        <f t="shared" si="132"/>
+        <v>1.1150714244161333</v>
+      </c>
+      <c r="R1263">
+        <f t="shared" si="133"/>
+        <v>-2.9738077095576632E-2</v>
+      </c>
+      <c r="S1263">
+        <f t="shared" si="134"/>
+        <v>1.4357143924349851E-2</v>
+      </c>
+      <c r="T1263">
+        <f t="shared" si="135"/>
+        <v>2.1535715886524776E-4</v>
+      </c>
+      <c r="U1263">
+        <f t="shared" si="136"/>
+        <v>-138.08724656413301</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1264" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B1264">
+        <v>1.0829999446868896</v>
+      </c>
+      <c r="C1264">
+        <v>1.1039999723434448</v>
+      </c>
+      <c r="D1264">
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="E1264">
+        <v>1.1009999513626099</v>
+      </c>
+      <c r="F1264">
+        <v>3120801</v>
+      </c>
+      <c r="G1264">
+        <v>31208.009765625</v>
+      </c>
+      <c r="H1264">
+        <f t="shared" si="144"/>
+        <v>1262</v>
+      </c>
+      <c r="I1264">
+        <f>SUM($F$3:F1264)/H1264</f>
+        <v>3994031.9863559827</v>
+      </c>
+      <c r="N1264">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1264">
+        <f t="shared" si="162"/>
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="P1264">
+        <f t="shared" si="143"/>
+        <v>1.0949999888737996</v>
+      </c>
+      <c r="Q1264">
+        <f t="shared" si="132"/>
+        <v>1.1099047575678145</v>
+      </c>
+      <c r="R1264">
+        <f t="shared" si="133"/>
+        <v>-1.4904768694014914E-2</v>
+      </c>
+      <c r="S1264">
+        <f t="shared" si="134"/>
+        <v>1.2251704728522281E-2</v>
+      </c>
+      <c r="T1264">
+        <f t="shared" si="135"/>
+        <v>1.8377557092783421E-4</v>
+      </c>
+      <c r="U1264">
+        <f t="shared" si="136"/>
+        <v>-81.103101020253575</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1265" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B1265">
+        <v>1.1080000400543213</v>
+      </c>
+      <c r="C1265">
+        <v>1.1080000400543213</v>
+      </c>
+      <c r="D1265">
+        <v>1.090999960899353</v>
+      </c>
+      <c r="E1265">
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="F1265">
+        <v>2451800</v>
+      </c>
+      <c r="G1265">
+        <v>24518</v>
+      </c>
+      <c r="H1265">
+        <f t="shared" si="144"/>
+        <v>1263</v>
+      </c>
+      <c r="I1265">
+        <f>SUM($F$3:F1265)/H1265</f>
+        <v>3992810.900064331</v>
+      </c>
+      <c r="N1265">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1265">
+        <f t="shared" si="162"/>
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="P1265">
+        <f t="shared" si="143"/>
+        <v>1.0990000168482463</v>
+      </c>
+      <c r="Q1265">
+        <f t="shared" si="132"/>
+        <v>1.1079999974795751</v>
+      </c>
+      <c r="R1265">
+        <f t="shared" si="133"/>
+        <v>-8.9999806313287856E-3</v>
+      </c>
+      <c r="S1265">
+        <f t="shared" si="134"/>
+        <v>1.2047617613863779E-2</v>
+      </c>
+      <c r="T1265">
+        <f t="shared" si="135"/>
+        <v>1.8071426420795668E-4</v>
+      </c>
+      <c r="U1265">
+        <f t="shared" si="136"/>
+        <v>-49.802270289920614</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1266" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1266">
+        <v>1.093000054359436</v>
+      </c>
+      <c r="C1266">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="D1266">
+        <v>1.0880000591278076</v>
+      </c>
+      <c r="E1266">
+        <v>1.0959999561309814</v>
+      </c>
+      <c r="F1266">
+        <v>1195000</v>
+      </c>
+      <c r="G1266">
+        <v>11950</v>
+      </c>
+      <c r="H1266">
+        <f t="shared" si="144"/>
+        <v>1264</v>
+      </c>
+      <c r="I1266">
+        <f>SUM($F$3:F1266)/H1266</f>
+        <v>3990597.4420737736</v>
+      </c>
+      <c r="N1266">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1266">
+        <f t="shared" si="162"/>
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="P1266">
+        <f t="shared" si="143"/>
+        <v>1.0943333307902019</v>
+      </c>
+      <c r="Q1266">
+        <f t="shared" si="132"/>
+        <v>1.1059999948456174</v>
+      </c>
+      <c r="R1266">
+        <f t="shared" si="133"/>
+        <v>-1.1666664055415499E-2</v>
+      </c>
+      <c r="S1266">
+        <f t="shared" si="134"/>
+        <v>1.2095237264827816E-2</v>
+      </c>
+      <c r="T1266">
+        <f t="shared" si="135"/>
+        <v>1.8142855897241723E-4</v>
+      </c>
+      <c r="U1266">
+        <f t="shared" si="136"/>
+        <v>-64.304451964418647</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1267" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1267">
+        <v>1.0859999656677246</v>
+      </c>
+      <c r="C1267">
+        <v>1.0959999561309814</v>
+      </c>
+      <c r="D1267">
+        <v>1.0850000381469727</v>
+      </c>
+      <c r="E1267">
+        <v>1.0880000591278076</v>
+      </c>
+      <c r="F1267">
+        <v>1650800</v>
+      </c>
+      <c r="G1267">
+        <v>16508</v>
+      </c>
+      <c r="H1267">
+        <f t="shared" si="144"/>
+        <v>1265</v>
+      </c>
+      <c r="I1267">
+        <f>SUM($F$3:F1267)/H1267</f>
+        <v>3988747.7998270751</v>
+      </c>
+      <c r="N1267">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1267">
+        <f t="shared" si="162"/>
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="P1267">
+        <f t="shared" si="143"/>
+        <v>1.0896666844685872</v>
+      </c>
+      <c r="Q1267">
+        <f t="shared" si="132"/>
+        <v>1.1029523781367712</v>
+      </c>
+      <c r="R1267">
+        <f t="shared" si="133"/>
+        <v>-1.3285693668183995E-2</v>
+      </c>
+      <c r="S1267">
+        <f t="shared" si="134"/>
+        <v>1.1380950609842946E-2</v>
+      </c>
+      <c r="T1267">
+        <f t="shared" si="135"/>
+        <v>1.7071425914764419E-4</v>
+      </c>
+      <c r="U1267">
+        <f t="shared" si="136"/>
+        <v>-77.824159121316924</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1268" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1268">
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="C1268">
+        <v>1.0850000381469727</v>
+      </c>
+      <c r="D1268">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="E1268">
+        <v>1.0809999704360962</v>
+      </c>
+      <c r="F1268">
+        <v>2369000</v>
+      </c>
+      <c r="G1268">
+        <v>23690</v>
+      </c>
+      <c r="H1268">
+        <f t="shared" si="144"/>
+        <v>1266</v>
+      </c>
+      <c r="I1268">
+        <f>SUM($F$3:F1268)/H1268</f>
+        <v>3987468.3781842417</v>
+      </c>
+      <c r="N1268">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1268">
+        <f t="shared" si="162"/>
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="P1268">
+        <f t="shared" si="143"/>
+        <v>1.0779999891916912</v>
+      </c>
+      <c r="Q1268">
+        <f t="shared" si="132"/>
+        <v>1.1002142855099268</v>
+      </c>
+      <c r="R1268">
+        <f t="shared" si="133"/>
+        <v>-2.2214296318235682E-2</v>
+      </c>
+      <c r="S1268">
+        <f t="shared" si="134"/>
+        <v>1.1816328885603911E-2</v>
+      </c>
+      <c r="T1268">
+        <f t="shared" si="135"/>
+        <v>1.7724493328405866E-4</v>
+      </c>
+      <c r="U1268">
+        <f t="shared" si="136"/>
+        <v>-125.33106536046539</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1269" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B1269">
+        <v>1.0690000057220459</v>
+      </c>
+      <c r="C1269">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="D1269">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="E1269">
+        <v>1.0709999799728394</v>
+      </c>
+      <c r="F1269">
+        <v>1463700</v>
+      </c>
+      <c r="G1269">
+        <v>14637</v>
+      </c>
+      <c r="H1269">
+        <f t="shared" si="144"/>
+        <v>1267</v>
+      </c>
+      <c r="I1269">
+        <f>SUM($F$3:F1269)/H1269</f>
+        <v>3985476.4536552881</v>
+      </c>
+      <c r="N1269">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1269">
+        <f t="shared" si="162"/>
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="P1269">
+        <f t="shared" si="143"/>
+        <v>1.0736666520436604</v>
+      </c>
+      <c r="Q1269">
+        <f t="shared" si="132"/>
+        <v>1.0978571403594244</v>
+      </c>
+      <c r="R1269">
+        <f t="shared" si="133"/>
+        <v>-2.4190488315763981E-2</v>
+      </c>
+      <c r="S1269">
+        <f t="shared" si="134"/>
+        <v>1.2741500828541879E-2</v>
+      </c>
+      <c r="T1269">
+        <f t="shared" si="135"/>
+        <v>1.9112251242812817E-4</v>
+      </c>
+      <c r="U1269">
+        <f t="shared" si="136"/>
+        <v>-126.57058558112477</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1270" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B1270">
+        <v>1.0700000524520874</v>
+      </c>
+      <c r="C1270">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="D1270">
+        <v>1.0590000152587891</v>
+      </c>
+      <c r="E1270">
+        <v>1.0590000152587891</v>
+      </c>
+      <c r="F1270">
+        <v>450800.96875</v>
+      </c>
+      <c r="G1270">
+        <v>4508.009765625</v>
+      </c>
+      <c r="H1270">
+        <f t="shared" si="144"/>
+        <v>1268</v>
+      </c>
+      <c r="I1270">
+        <f>SUM($F$3:F1270)/H1270</f>
+        <v>3982688.8546924288</v>
+      </c>
+      <c r="N1270">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1270">
+        <f t="shared" si="162"/>
+        <v>1.0590000152587891</v>
+      </c>
+      <c r="P1270">
+        <f t="shared" si="143"/>
+        <v>1.0646666685740154</v>
+      </c>
+      <c r="Q1270">
+        <f t="shared" si="132"/>
+        <v>1.0942857123556591</v>
+      </c>
+      <c r="R1270">
+        <f t="shared" si="133"/>
+        <v>-2.9619043781643706E-2</v>
+      </c>
+      <c r="S1270">
+        <f t="shared" si="134"/>
+        <v>1.300000292914256E-2</v>
+      </c>
+      <c r="T1270">
+        <f t="shared" si="135"/>
+        <v>1.950000439371384E-4</v>
+      </c>
+      <c r="U1270">
+        <f t="shared" si="136"/>
+        <v>-151.89249798934358</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1271" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B1271">
+        <v>1.0590000152587891</v>
+      </c>
+      <c r="C1271">
+        <v>1.0700000524520874</v>
+      </c>
+      <c r="D1271">
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="E1271">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="F1271">
+        <v>1331802</v>
+      </c>
+      <c r="G1271">
+        <v>13318.01953125</v>
+      </c>
+      <c r="H1271">
+        <f t="shared" si="144"/>
+        <v>1269</v>
+      </c>
+      <c r="I1271">
+        <f>SUM($F$3:F1271)/H1271</f>
+        <v>3980599.897360126</v>
+      </c>
+      <c r="N1271">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1271">
+        <f t="shared" si="162"/>
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="P1271">
+        <f t="shared" si="143"/>
+        <v>1.062666654586792</v>
+      </c>
+      <c r="Q1271">
+        <f t="shared" si="132"/>
+        <v>1.0901666624205453</v>
+      </c>
+      <c r="R1271">
+        <f t="shared" si="133"/>
+        <v>-2.7500007833753282E-2</v>
+      </c>
+      <c r="S1271">
+        <f t="shared" si="134"/>
+        <v>1.2809525541707778E-2</v>
+      </c>
+      <c r="T1271">
+        <f t="shared" si="135"/>
+        <v>1.9214288312561665E-4</v>
+      </c>
+      <c r="U1271">
+        <f t="shared" si="136"/>
+        <v>-143.12269799644199</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1272" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B1272">
+        <v>1.0700000524520874</v>
+      </c>
+      <c r="C1272">
+        <v>1.0839999914169312</v>
+      </c>
+      <c r="D1272">
+        <v>1.065000057220459</v>
+      </c>
+      <c r="E1272">
+        <v>1.0659999847412109</v>
+      </c>
+      <c r="F1272">
+        <v>1323200</v>
+      </c>
+      <c r="G1272">
+        <v>13232</v>
+      </c>
+      <c r="H1272">
+        <f t="shared" si="144"/>
+        <v>1270</v>
+      </c>
+      <c r="I1272">
+        <f>SUM($F$3:F1272)/H1272</f>
+        <v>3978507.4564960632</v>
+      </c>
+      <c r="N1272">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1272">
+        <f t="shared" si="162"/>
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="P1272">
+        <f t="shared" si="143"/>
+        <v>1.071666677792867</v>
+      </c>
+      <c r="Q1272">
+        <f t="shared" si="132"/>
+        <v>1.08659523441678</v>
+      </c>
+      <c r="R1272">
+        <f t="shared" si="133"/>
+        <v>-1.4928556623913014E-2</v>
+      </c>
+      <c r="S1272">
+        <f t="shared" si="134"/>
+        <v>1.1938773855871086E-2</v>
+      </c>
+      <c r="T1272">
+        <f t="shared" si="135"/>
+        <v>1.7908160783806627E-4</v>
+      </c>
+      <c r="U1272">
+        <f t="shared" si="136"/>
+        <v>-83.36175224321245</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1273" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1273">
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="C1273">
+        <v>1.0870000123977661</v>
+      </c>
+      <c r="D1273">
+        <v>1.065000057220459</v>
+      </c>
+      <c r="E1273">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="F1273">
+        <v>1525700</v>
+      </c>
+      <c r="G1273">
+        <v>15257</v>
+      </c>
+      <c r="H1273">
+        <f t="shared" si="144"/>
+        <v>1271</v>
+      </c>
+      <c r="I1273">
+        <f>SUM($F$3:F1273)/H1273</f>
+        <v>3976577.6315892995</v>
+      </c>
+      <c r="N1273">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1273">
+        <f t="shared" si="162"/>
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="P1273">
+        <f t="shared" si="143"/>
+        <v>1.0780000289281209</v>
+      </c>
+      <c r="Q1273">
+        <f t="shared" si="132"/>
+        <v>1.0843809530848549</v>
+      </c>
+      <c r="R1273">
+        <f t="shared" si="133"/>
+        <v>-6.3809241567340802E-3</v>
+      </c>
+      <c r="S1273">
+        <f t="shared" si="134"/>
+        <v>1.1088435341711746E-2</v>
+      </c>
+      <c r="T1273">
+        <f t="shared" si="135"/>
+        <v>1.6632653012567619E-4</v>
+      </c>
+      <c r="U1273">
+        <f t="shared" si="136"/>
+        <v>-38.363838600568769</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1274" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1274">
+        <v>1.093999981880188</v>
+      </c>
+      <c r="C1274">
+        <v>1.0950000286102295</v>
+      </c>
+      <c r="D1274">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="E1274">
+        <v>1.0870000123977661</v>
+      </c>
+      <c r="F1274">
+        <v>955600</v>
+      </c>
+      <c r="G1274">
+        <v>9556</v>
+      </c>
+      <c r="H1274">
+        <f t="shared" si="144"/>
+        <v>1272</v>
+      </c>
+      <c r="I1274">
+        <f>SUM($F$3:F1274)/H1274</f>
+        <v>3974202.6491745282</v>
+      </c>
+      <c r="N1274">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1274">
+        <f t="shared" si="162"/>
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="P1274">
+        <f t="shared" si="143"/>
+        <v>1.0880000193913777</v>
+      </c>
+      <c r="Q1274">
+        <f t="shared" si="132"/>
+        <v>1.082690477371216</v>
+      </c>
+      <c r="R1274">
+        <f t="shared" si="133"/>
+        <v>5.3095420201616506E-3</v>
+      </c>
+      <c r="S1274">
+        <f t="shared" si="134"/>
+        <v>9.6394561585925499E-3</v>
+      </c>
+      <c r="T1274">
+        <f t="shared" si="135"/>
+        <v>1.4459184237888825E-4</v>
+      </c>
+      <c r="U1274">
+        <f t="shared" si="136"/>
+        <v>36.720896094874661</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1275" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1275">
+        <v>1.0900000333786011</v>
+      </c>
+      <c r="C1275">
+        <v>1.1089999675750732</v>
+      </c>
+      <c r="D1275">
+        <v>1.0809999704360962</v>
+      </c>
+      <c r="E1275">
+        <v>1.0880000591278076</v>
+      </c>
+      <c r="F1275">
+        <v>1567500</v>
+      </c>
+      <c r="G1275">
+        <v>15675</v>
+      </c>
+      <c r="H1275">
+        <f t="shared" si="144"/>
+        <v>1273</v>
+      </c>
+      <c r="I1275">
+        <f>SUM($F$3:F1275)/H1275</f>
+        <v>3972312.0736449333</v>
+      </c>
+      <c r="N1275">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1275">
+        <f t="shared" si="162"/>
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="P1275">
+        <f t="shared" si="143"/>
+        <v>1.0926666657129924</v>
+      </c>
+      <c r="Q1275">
+        <f t="shared" si="132"/>
+        <v>1.0828809539477031</v>
+      </c>
+      <c r="R1275">
+        <f t="shared" si="133"/>
+        <v>9.7857117652893066E-3</v>
+      </c>
+      <c r="S1275">
+        <f t="shared" si="134"/>
+        <v>9.8027217955816304E-3</v>
+      </c>
+      <c r="T1275">
+        <f t="shared" si="135"/>
+        <v>1.4704082693372446E-4</v>
+      </c>
+      <c r="U1275">
+        <f t="shared" si="136"/>
+        <v>66.550984303835619</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1276" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1276">
+        <v>1.0950000286102295</v>
+      </c>
+      <c r="C1276">
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="D1276">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="E1276">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="F1276">
+        <v>615700</v>
+      </c>
+      <c r="G1276">
+        <v>6157</v>
+      </c>
+      <c r="H1276">
+        <f t="shared" si="144"/>
+        <v>1274</v>
+      </c>
+      <c r="I1276">
+        <f>SUM($F$3:F1276)/H1276</f>
+        <v>3969677.3702904237</v>
+      </c>
+      <c r="N1276">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1276">
+        <f t="shared" si="162"/>
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="P1276">
+        <f t="shared" si="143"/>
+        <v>1.08733336130778</v>
+      </c>
+      <c r="Q1276">
+        <f t="shared" si="132"/>
+        <v>1.0828571489879064</v>
+      </c>
+      <c r="R1276">
+        <f t="shared" si="133"/>
+        <v>4.476212319873607E-3</v>
+      </c>
+      <c r="S1276">
+        <f t="shared" si="134"/>
+        <v>9.782317544327299E-3</v>
+      </c>
+      <c r="T1276">
+        <f t="shared" si="135"/>
+        <v>1.4673476316490948E-4</v>
+      </c>
+      <c r="U1276">
+        <f t="shared" si="136"/>
+        <v>30.505465939539949</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1277" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1277">
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="C1277">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="D1277">
+        <v>1.0570000410079956</v>
+      </c>
+      <c r="E1277">
+        <v>1.0579999685287476</v>
+      </c>
+      <c r="F1277">
+        <v>1293200</v>
+      </c>
+      <c r="G1277">
+        <v>12932</v>
+      </c>
+      <c r="H1277">
+        <f t="shared" si="144"/>
+        <v>1275</v>
+      </c>
+      <c r="I1277">
+        <f>SUM($F$3:F1277)/H1277</f>
+        <v>3967578.1723529412</v>
+      </c>
+      <c r="N1277">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1277">
+        <f t="shared" si="162"/>
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="P1277">
+        <f t="shared" si="143"/>
+        <v>1.0633333524068196</v>
+      </c>
+      <c r="Q1277">
+        <f t="shared" si="132"/>
+        <v>1.0812857207797824</v>
+      </c>
+      <c r="R1277">
+        <f t="shared" si="133"/>
+        <v>-1.7952368372962768E-2</v>
+      </c>
+      <c r="S1277">
+        <f t="shared" si="134"/>
+        <v>1.1000003133501341E-2</v>
+      </c>
+      <c r="T1277">
+        <f t="shared" si="135"/>
+        <v>1.6500004700252012E-4</v>
+      </c>
+      <c r="U1277">
+        <f t="shared" si="136"/>
+        <v>-108.80220156960667</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1278" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1278">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C1278">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="D1278">
+        <v>1.0180000066757202</v>
+      </c>
+      <c r="E1278">
+        <v>1.0199999809265137</v>
+      </c>
+      <c r="F1278">
+        <v>3735500</v>
+      </c>
+      <c r="G1278">
+        <v>37355</v>
+      </c>
+      <c r="H1278">
+        <f t="shared" si="144"/>
+        <v>1276</v>
+      </c>
+      <c r="I1278">
+        <f>SUM($F$3:F1278)/H1278</f>
+        <v>3967396.2929075235</v>
+      </c>
+      <c r="N1278">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1278">
+        <f t="shared" si="162"/>
+        <v>1.0180000066757202</v>
+      </c>
+      <c r="P1278">
+        <f t="shared" si="143"/>
+        <v>1.0286666552225749</v>
+      </c>
+      <c r="Q1278">
+        <f t="shared" si="132"/>
+        <v>1.0765476255189805</v>
+      </c>
+      <c r="R1278">
+        <f t="shared" si="133"/>
+        <v>-4.7880970296405589E-2</v>
+      </c>
+      <c r="S1278">
+        <f t="shared" si="134"/>
+        <v>1.3517013212450515E-2</v>
+      </c>
+      <c r="T1278">
+        <f t="shared" si="135"/>
+        <v>2.0275519818675771E-4</v>
+      </c>
+      <c r="U1278">
+        <f t="shared" si="136"/>
+        <v>-236.15162878488792</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1279" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1279">
+        <v>1.0169999599456787</v>
+      </c>
+      <c r="C1279">
+        <v>1.0260000228881836</v>
+      </c>
+      <c r="D1279">
+        <v>1.0169999599456787</v>
+      </c>
+      <c r="E1279">
+        <v>1.0210000276565552</v>
+      </c>
+      <c r="F1279">
+        <v>2711800</v>
+      </c>
+      <c r="G1279">
+        <v>27118</v>
+      </c>
+      <c r="H1279">
+        <f t="shared" si="144"/>
+        <v>1277</v>
+      </c>
+      <c r="I1279">
+        <f>SUM($F$3:F1279)/H1279</f>
+        <v>3966413.0538371182</v>
+      </c>
+      <c r="N1279">
+        <f t="shared" si="161"/>
+        <v>1.128000020980835</v>
+      </c>
+      <c r="O1279">
+        <f t="shared" si="162"/>
+        <v>1.0169999599456787</v>
+      </c>
+      <c r="P1279">
+        <f t="shared" si="143"/>
+        <v>1.0213333368301392</v>
+      </c>
+      <c r="Q1279">
+        <f t="shared" si="132"/>
+        <v>1.0710000055176871</v>
+      </c>
+      <c r="R1279">
+        <f t="shared" si="133"/>
+        <v>-4.9666668687547988E-2</v>
+      </c>
+      <c r="S1279">
+        <f t="shared" si="134"/>
+        <v>1.6333337138299209E-2</v>
+      </c>
+      <c r="T1279">
+        <f t="shared" si="135"/>
+        <v>2.4500005707448814E-4</v>
+      </c>
+      <c r="U1279">
+        <f t="shared" si="136"/>
+        <v>-202.72104945856267</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1279"/>
+  <dimension ref="A1:U1280"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -4617,7 +4617,7 @@
         <v>-43.871095294582702</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>44466</v>
       </c>
@@ -4647,6 +4647,12 @@
         <f>SUM($F$3:F66)/H66</f>
         <v>16912348.84375</v>
       </c>
+      <c r="K66" s="2">
+        <v>46325</v>
+      </c>
+      <c r="L66" s="2">
+        <v>46303</v>
+      </c>
       <c r="N66">
         <f t="shared" si="11"/>
         <v>0.98799999999999999</v>
@@ -65833,23 +65839,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1279" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1280" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1279" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1280" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1279" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1280" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1279" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1280" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1279" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1280" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68979,7 +68985,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1279" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1280" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69089,7 +69095,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1279" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1280" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -79870,11 +79876,11 @@
         <v>3999276.1254222975</v>
       </c>
       <c r="N1260">
-        <f t="shared" ref="N1260:N1279" si="161">IF(A1260&lt;&gt;$K$65,MAX(N1259,VLOOKUP(A1260,A:C,3)),)</f>
+        <f t="shared" ref="N1260:N1280" si="161">IF(A1260&lt;&gt;$K$65,MAX(N1259,VLOOKUP(A1260,A:C,3)),)</f>
         <v>1.128000020980835</v>
       </c>
       <c r="O1260">
-        <f t="shared" ref="O1260:O1279" si="162">IF(A1260&lt;&gt;$K$65,MIN(O1259,VLOOKUP(A1260,A:D,4)),)</f>
+        <f t="shared" ref="O1260:O1280" si="162">IF(A1260&lt;&gt;$K$65,MIN(O1259,VLOOKUP(A1260,A:D,4)),)</f>
         <v>1.0989999771118164</v>
       </c>
       <c r="P1260">
@@ -81097,6 +81103,69 @@
       <c r="U1279">
         <f t="shared" si="136"/>
         <v>-202.72104945856267</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1280" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1280">
+        <v>1.0199999809265137</v>
+      </c>
+      <c r="C1280">
+        <v>1.0279999971389771</v>
+      </c>
+      <c r="D1280">
+        <v>1.0199999809265137</v>
+      </c>
+      <c r="E1280">
+        <v>1.0230000019073486</v>
+      </c>
+      <c r="F1280">
+        <v>2464000</v>
+      </c>
+      <c r="G1280">
+        <v>24640</v>
+      </c>
+      <c r="H1280">
+        <f t="shared" si="144"/>
+        <v>1278</v>
+      </c>
+      <c r="I1280">
+        <f>SUM($F$3:F1280)/H1280</f>
+        <v>3965237.4567683879</v>
+      </c>
+      <c r="N1280">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
+      <c r="O1280">
+        <f t="shared" si="162"/>
+        <v>0</v>
+      </c>
+      <c r="P1280">
+        <f t="shared" si="143"/>
+        <v>1.0236666599909465</v>
+      </c>
+      <c r="Q1280">
+        <f t="shared" si="132"/>
+        <v>1.065952386174883</v>
+      </c>
+      <c r="R1280">
+        <f t="shared" si="133"/>
+        <v>-4.2285726183936445E-2</v>
+      </c>
+      <c r="S1280">
+        <f t="shared" si="134"/>
+        <v>1.8768712776858796E-2</v>
+      </c>
+      <c r="T1280">
+        <f t="shared" si="135"/>
+        <v>2.8153069165288194E-4</v>
+      </c>
+      <c r="U1280">
+        <f t="shared" si="136"/>
+        <v>-150.19934748738993</v>
       </c>
     </row>
   </sheetData>
